--- a/Test Cases/Candidate Application Form.xlsx
+++ b/Test Cases/Candidate Application Form.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase1" sheetId="1" r:id="rId1"/>
-    <sheet name="Phase2" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Phase1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Phase2" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1232">
   <si>
     <t>S.No</t>
   </si>
@@ -65,7 +65,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Verify the Mankind header logo is visible
 3. Verify the page title "Application Form - Phase 1"
 4. Verify the account icon and "Sign out" button are present
@@ -91,7 +91,7 @@
     <t>Verifying that the section heading and all field labels/button text in 1.1 Basic Info are present and correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Verify the section heading "1.1 Basic Info"
 3. Verify field labels: "First Name (As per Aadhaar)*", "Middle Name", "Last Name*", "Division", "Role*", "HQ Preference*"
 4. Verify radio button labels: "HQ Flexible", "HQ Not Flexible"</t>
@@ -112,7 +112,7 @@
     <t>Verifying that the section heading and all field labels in 1.2 Personal Details and its Communication Address sub-section (Permanent + Current Address blocks) are present and correctly worded. Note: the live page currently reads "Enter father's net earning / month" for Father's Net Earning but "Enter mother's net worth / month" for Mother's (worth vs earning) - flagging this inconsistency for confirmation rather than assuming it is intentional; asserting the current live wording for now.</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Verify the section heading "1.2 Personal Details"
 3. Verify field labels: "Aadhaar Number*", "Pan Card Number*", "Mobile Number*", "Email ID*", "Gender*", "Date of Birth*", "Marital Status*", "Father's Name*", "Occupation*" (Father's), "Net Earning / Month*" (Father's), "Mother's Name*", "Occupation*" (Mother's), "Net Earning / Month*" (Mother's)
 4. Verify the sub-heading "Communication Address"
@@ -142,7 +142,7 @@
     <t>Verifying that the section heading, both Yes/No questions, their conditional field labels, and the Save/Next buttons are present and correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Verify the section heading "1.3 General Details"
 3. Verify the question "Do you have your own vehicle?" with "Yes"/"No" radio options, and the "Vehicle No." field label
 4. Verify the question "Have you ever given interview in Mankind Pharma Ltd. in the past?" with "Yes"/"No" radio options, and the "Interview Date" field label
@@ -170,7 +170,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details left incomplete (not all mandatory fields filled/validated)</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page with Personal Details left incomplete
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page with Personal Details left incomplete
 2. Attempt to click "2. Qualification Details" in the step indicator
 3. Attempt to click "3. Experience Details" in the step indicator
 4. Verify neither step opens</t>
@@ -191,7 +191,7 @@
     <t>Verifying that clicking the +/- toggle on the "1.1 Basic Info" section header correctly collapses (hides) and expands (shows) that section's fields</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Locate the "1.1 Basic Info" section header's toggle icon
 3. Click the toggle to collapse the section; verify its fields are hidden and the icon changes to "+"
 4. Click the toggle again to expand the section; verify its fields reappear and the icon changes to "-"</t>
@@ -212,7 +212,7 @@
     <t>Verifying that leaving First Name blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "First Name (As per Aadhaar)" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for First Name</t>
@@ -233,7 +233,7 @@
     <t>Verifying that leaving Last Name blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Last Name" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Last Name</t>
@@ -254,7 +254,7 @@
     <t>Verifying that leaving HQ Preference unselected is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "HQ Preference" unselected
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for HQ Preference</t>
@@ -275,7 +275,7 @@
     <t>Verifying that the Role dropdown lists exactly the expected options, correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Click the Role dropdown
 3. Verify the list of options shown</t>
   </si>
@@ -295,7 +295,7 @@
     <t>Verifying that a malformed PAN Card Number is rejected - a real Indian PAN is 5 letters + 4 digits + 1 letter (e.g. ABCDE1234F)</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Enter a malformed value into PAN Card Number (e.g. wrong length or wrong letter/digit pattern)
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for PAN Card Number</t>
@@ -316,7 +316,7 @@
     <t>Verifying that a Mobile Number with fewer or more than 10 digits is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Enter a Mobile Number with fewer than 10 digits (or more than 10)
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Mobile Number</t>
@@ -337,7 +337,7 @@
     <t>Verifying that a Date of Birth resulting in an age under 18 is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Enter a Date of Birth that makes the candidate younger than 18 today
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Date of Birth</t>
@@ -358,7 +358,7 @@
     <t>Verifying that the Gender dropdown lists exactly the expected options, correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Click the Gender dropdown
 3. Verify the list of options shown</t>
   </si>
@@ -378,7 +378,7 @@
     <t>Verifying that the Marital Status dropdown lists exactly the expected options, correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Click the Marital Status dropdown
 3. Verify the list of options shown</t>
   </si>
@@ -398,7 +398,7 @@
     <t>Verifying that leaving Father's Name blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Father's Name" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Father's Name</t>
@@ -419,7 +419,7 @@
     <t>Verifying that leaving Father's Occupation blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave Father's "Occupation" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Father's Occupation</t>
@@ -440,7 +440,7 @@
     <t>Verifying that leaving Father's Net Earning / Month blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave Father's "Net Earning / Month" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Father's Net Earning</t>
@@ -461,7 +461,7 @@
     <t>Verifying that leaving Mother's Name blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Mother's Name" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Mother's Name</t>
@@ -482,7 +482,7 @@
     <t>Verifying that leaving Mother's Occupation blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave Mother's "Occupation" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Mother's Occupation</t>
@@ -503,7 +503,7 @@
     <t>Verifying that leaving Mother's Net Earning / Month blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave Mother's "Net Earning / Month" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Mother's Net Earning</t>
@@ -524,7 +524,7 @@
     <t>Verifying that leaving Permanent Address blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Permanent Address" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Permanent Address</t>
@@ -545,7 +545,7 @@
     <t>Verifying that leaving the Permanent Address block's City blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave the Permanent Address block's "City" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for City</t>
@@ -566,7 +566,7 @@
     <t>Verifying that an invalid Pin Code in the Permanent Address block is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Enter an invalid Pin Code into the Permanent Address block's "Pin Code" field (e.g. wrong digit count)
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Pin Code</t>
@@ -587,7 +587,7 @@
     <t>Verifying that checking "Same as Permanent" auto-fills the Current Address block (Current Address, Address Line 2, Address Line 3, City, Pin Code, State, District) with the same values already entered in the Permanent Address block</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Fill the Permanent Address block completely (Permanent Address, Address Line 2, Address Line 3, City, Pin Code, State, District)
 3. Check "Same as Permanent"
 4. Verify the Current Address block's fields</t>
@@ -611,7 +611,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | "Same as Permanent" left unchecked</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked and leave "Current Address" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Current Address</t>
@@ -632,7 +632,7 @@
     <t>Verifying that leaving the Current Address block's City blank (with "Same as Permanent" unchecked) is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked and leave the Current Address block's "City" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for City</t>
@@ -653,7 +653,7 @@
     <t>Verifying that leaving the Current Address block's Pin Code blank (with "Same as Permanent" unchecked) is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked and leave the Current Address block's "Pin Code" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Pin Code</t>
@@ -674,7 +674,7 @@
     <t>Verifying that the State dropdown (Permanent Address block) offers exactly the 26 entries the application is designed to provide, correctly worded and in the expected order. Confirmed 2026-09-18 from screenshots of the live dropdown: the list is intentionally limited to these 26 - it is NOT meant to carry all 28 Indian states and 8 union territories.</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Click the State dropdown (Permanent Address block)
 3. Verify the list of options shown against the current official list of India's 28 states and 8 union territories</t>
   </si>
@@ -694,7 +694,7 @@
     <t>Verifying the District dropdown (Permanent Address block) is empty/disabled until a State is chosen, then cascades to show only that specific state's districts. Exact per-state district lists need live confirmation when this test case is automated.</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Before selecting a State, check the District dropdown (Permanent Address block) - verify it is empty or disabled
 3. Select a State
 4. Click the District dropdown and verify it now lists districts belonging only to that selected state</t>
@@ -715,7 +715,7 @@
     <t>Verifying that clicking the +/- toggle on the "1.2 Personal Details" section header correctly collapses (hides) and expands (shows) that section's fields</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Locate the "1.2 Personal Details" section header's toggle icon
 3. Click the toggle to collapse the section; verify its fields are hidden and the icon changes to "+"
 4. Click the toggle again to expand the section; verify its fields reappear and the icon changes to "-"</t>
@@ -733,7 +733,7 @@
     <t>Verifying that clicking the +/- toggle on the "1.3 General Details" section header correctly collapses (hides) and expands (shows) that section's fields</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Locate the "1.3 General Details" section header's toggle icon
 3. Click the toggle to collapse the section; verify its fields are hidden and the icon changes to "+"
 4. Click the toggle again to expand the section; verify its fields reappear and the icon changes to "-"</t>
@@ -751,7 +751,7 @@
     <t>Verifying that the Vehicle No. field stays disabled/read-only and rejects text entry when the "No" option is selected for the vehicle question</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Under "Do you have your own vehicle?", select "No"
 3. Attempt to click into the "Vehicle No." field and type a value</t>
   </si>
@@ -771,7 +771,7 @@
     <t>Verifying that selecting "Yes" for the vehicle question enables the Vehicle No. field for input and makes it mandatory to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Under "Do you have your own vehicle?", select "Yes"
 3. Verify the "Vehicle No." field becomes enabled for typing
 4. Leave "Vehicle No." blank and attempt to proceed (click Next or Save)
@@ -793,7 +793,7 @@
     <t>Verifying that the Interview Date field stays disabled/read-only and rejects entry when the "No" option is selected for the past-interview question</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Under "Have you ever given interview in Mankind Pharma Ltd. in the past?", select "No"
 3. Attempt to click into the "Interview Date" field and set a value</t>
   </si>
@@ -813,7 +813,7 @@
     <t>Verifying that selecting "Yes" for the past-interview question enables the Interview Date field for input. Note: whether Interview Date is mandatory in this state has not been confirmed by the user yet, so this test only asserts the field becomes enabled/enterable, not a mandatory requirement.</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Under "Have you ever given interview in Mankind Pharma Ltd. in the past?", select "Yes"
 3. Verify the "Interview Date" field becomes enabled
 4. Select a valid date and verify it is accepted</t>
@@ -837,7 +837,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | All mandatory fields in 1.1 Basic Info, 1.2 Personal Details, and 1.3 General Details are validly filled</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Fill every mandatory field in 1.1 Basic Info, 1.2 Personal Details, and 1.3 General Details with valid data
 3. Click "Next"
 4. Verify the "2. Qualification Details" section renders</t>
@@ -858,7 +858,7 @@
     <t>Verifying that clicking Sign Out from the Application Form - Phase 1 page correctly ends the candidate's session</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Click the "Sign Out" button
 3. Verify the candidate is redirected away from the application form (e.g. to the Sign In page)
 4. Attempt to navigate back to the Application Form page directly
@@ -880,7 +880,7 @@
     <t>Verifying that data entered into Phase 1 fields and saved via the Save button is retained and auto-filled back into those fields after the page is refreshed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Fill in a set of fields across 1.1 Basic Info, 1.2 Personal Details, and 1.3 General Details
 3. Click "Save"
 4. Refresh the page
@@ -905,7 +905,7 @@
     <t>Verifying that leaving Mobile Number blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Mobile Number" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Mobile Number</t>
@@ -926,7 +926,7 @@
     <t>Verifying that leaving PAN Card Number blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "PAN Card Number" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for PAN Card Number</t>
@@ -950,7 +950,7 @@
     <t>Verifying that leaving Date of Birth blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Date of Birth" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Date of Birth</t>
@@ -971,7 +971,7 @@
     <t>Verifying that leaving Gender blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Gender" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Gender</t>
@@ -992,7 +992,7 @@
     <t>Verifying that leaving Marital Status blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Marital Status" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Marital Status</t>
@@ -1013,7 +1013,7 @@
     <t>Verifying that leaving the Permanent Address block's State blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave the Permanent Address block's "State" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for State</t>
@@ -1034,7 +1034,7 @@
     <t>Verifying that leaving the Permanent Address block's District blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Select a State but leave the Permanent Address block's "District" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for District</t>
@@ -1055,7 +1055,7 @@
     <t>Verifying that the State dropdown in the Current Address block (with "Same as Permanent" unchecked) offers exactly the same 26 entries as the Permanent Address block, correctly worded and in the expected order. Confirmed 2026-09-18 from screenshots of the live dropdown: the list is intentionally limited to these 26.</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked
 3. Click the State dropdown (Current Address block)
 4. Verify the list of options shown against the current official list of India's 28 states and 8 union territories</t>
@@ -1076,7 +1076,7 @@
     <t>Verifying the District dropdown in the Current Address block (with "Same as Permanent" unchecked) is empty/disabled until a State is chosen, then cascades to show only that specific state's districts. Exact per-state district lists need live confirmation when this test case is automated.</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked
 3. Before selecting a State, check the District dropdown (Current Address block) - verify it is empty or disabled
 4. Select a State
@@ -1098,7 +1098,7 @@
     <t>Verifying that leaving the Current Address block's State blank (with "Same as Permanent" unchecked) is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked and leave the Current Address block's "State" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for State</t>
@@ -1119,7 +1119,7 @@
     <t>Verifying that leaving the Current Address block's District blank (with "Same as Permanent" unchecked) is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Application Form - Phase 1 page
+    <t xml:space="preserve">1. Reach the Application Form - Phase 1 page
 2. Leave "Same as Permanent" unchecked, select a State but leave the Current Address block's "District" blank
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for District</t>
@@ -1143,7 +1143,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details, General Details fully and validly completed</t>
   </si>
   <si>
-    <t>1. Complete Basic Info, Personal Details, and General Details with valid data
+    <t xml:space="preserve">1. Complete Basic Info, Personal Details, and General Details with valid data
 2. Click "Next"
 3. Verify the step indicator shows "2. Qualification Details" as the current step
 4. Verify the 10th, 12th, and Graduation sections are visible</t>
@@ -1167,7 +1167,7 @@
     <t>Verifying the section headings, field labels, and buttons on the Qualification Details page are present and correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Verify section headings "10th", "12th", "Graduation"
 3. Verify 10th/12th field labels: "From", "To", "Specialization", "% Of Marks"
 4. Verify Graduation field labels: "Course*", "From*", "To*", "Type*", "Specialization", "% Of Marks*"
@@ -1190,7 +1190,7 @@
     <t>Verifying step 1 (Personal Details) shows as completed with a checkmark, step 2 (Qualification Details) shows as the current/active step, and step 3 (Experience Details) shows as not-yet-reached</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Verify the visual state of all 3 step-indicator items</t>
   </si>
   <si>
@@ -1209,7 +1209,7 @@
     <t>Verifying that clicking the +/- toggle on each section header (10th, 12th, Graduation) correctly collapses and expands that section's fields, matching the same toggle pattern used in Personal Details</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. For each of "10th", "12th", "Graduation": click its toggle to collapse, verify fields hidden and icon changes to "+"; click again to expand, verify fields reappear and icon changes to "-"</t>
   </si>
   <si>
@@ -1228,7 +1228,7 @@
     <t>Verifying that leaving all 10th fields (From, To, Specialization, % Of Marks) blank does not block proceeding, since none of them are mandatory</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave the entire "10th" section blank
 3. Fill 12th (optional, can also be left blank) and Graduation (mandatory) with valid data
 4. Click "Next"</t>
@@ -1249,7 +1249,7 @@
     <t>Verifying that a 10th % Of Marks value below 2 or above 100 is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a 10th "% Of Marks" value outside [2, 100] (e.g. 1 or 101)
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for % Of Marks</t>
@@ -1270,7 +1270,7 @@
     <t>Verifying that a decimal % Of Marks value (e.g. 78.00) within [2, 100] is accepted for 10th</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a valid decimal value (e.g. "78.00") into 10th's "% Of Marks"
 3. Verify it is accepted without a validation error</t>
   </si>
@@ -1290,7 +1290,7 @@
     <t>Verifying that a 10th "To" date earlier than or equal to "From" is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a 10th "From" date, and a "To" date that is earlier than or equal to it
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1311,7 +1311,7 @@
     <t>Verifying that a 10th "From" or "To" date set in the future is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a future date (e.g. next year) into 10th's "From" or "To"
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1332,7 +1332,7 @@
     <t>Verifying that leaving all 12th fields blank does not block proceeding, since none of them are mandatory</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave the entire "12th" section blank
 3. Fill Graduation (mandatory) with valid data
 4. Click "Next"</t>
@@ -1353,7 +1353,7 @@
     <t>Verifying that a 12th % Of Marks value below 2 or above 100 is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a 12th "% Of Marks" value outside [2, 100]
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1374,7 +1374,7 @@
     <t>Verifying that a decimal % Of Marks value within [2, 100] is accepted for 12th</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a valid decimal value into 12th's "% Of Marks"
 3. Verify it is accepted</t>
   </si>
@@ -1394,7 +1394,7 @@
     <t>Verifying that a 12th "To" date earlier than or equal to "From" is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a 12th "From" date, and a "To" date earlier than or equal to it
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1415,7 +1415,7 @@
     <t>Verifying that a 12th "From" or "To" date set in the future is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a future date into 12th's "From" or "To"
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1436,7 +1436,7 @@
     <t>Verifying the chronological rule between 10th and 12th: 12th's "From" date must be strictly AFTER 10th's "To" date, i.e. a 12th start date that is prior to OR equal to 10th's end date should be rejected. The app does show a message for this rule ("12th start date can not be prior to 10th end date.") but root-cause probing shows it is driven by the WRONG field - see Actual Result.</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill 10th with a valid From/To range
 3. Fill 12th so that its "From" is NOT strictly after 10th's "To". Cover all violating shapes:
    (a) 12th range entirely before 10th's range
@@ -1450,7 +1450,7 @@
     <t>Every case where 12th's "From" is not strictly after 10th's "To" should be rejected with "12th start date can not be prior to 10th end date." and the form should not advance - including overlapping ranges and a 12th "From" exactly equal to 10th's "To".</t>
   </si>
   <si>
-    <t>FAILED - root cause identified: the validation compares the WRONG FIELD. It fires on 12th's END date vs 10th's END date, not on 12th's START date vs 10th's end date as the message claims. Net effect: the intended rule is not enforced at all, and a different, incorrect rule is enforced in its place.
+    <t xml:space="preserve">FAILED - root cause identified: the validation compares the WRONG FIELD. It fires on 12th's END date vs 10th's END date, not on 12th's START date vs 10th's end date as the message claims. Net effect: the intended rule is not enforced at all, and a different, incorrect rule is enforced in its place.
 Verified live 2026-09-23 across four dedicated probes (10th / 12th ranges, and whether Next was blocked):
   1. 11/09/2030-18/09/2031 / 11/09/2028-11/09/2029 (12th entirely before 10th) -&gt; REJECTED, message shown. [12th end 2029 &lt; 10th end 2031]
   2. 02/02/2010-02/02/2013 / 02/02/2011-02/02/2014 (overlapping) -&gt; ACCEPTED, advanced to Experience Details, despite 12th starting 2 years before 10th ended. [12th end 2014 &gt; 10th end 2013]
@@ -1471,7 +1471,7 @@
     <t>Verifying that leaving Graduation's Course dropdown unselected is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave Graduation's "Course" unselected
 3. Attempt to proceed (click Next or Save)
 4. Verify a validation message appears for Course</t>
@@ -1492,7 +1492,7 @@
     <t>Verifying that leaving Graduation's "From" date blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave Graduation's "From" date blank
 3. Attempt to proceed
 4. Verify a validation message appears for From</t>
@@ -1513,7 +1513,7 @@
     <t>Verifying that leaving Graduation's "To" date blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave Graduation's "To" date blank
 3. Attempt to proceed
 4. Verify a validation message appears for To</t>
@@ -1534,7 +1534,7 @@
     <t>Verifying that leaving Graduation's Type dropdown unselected is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave Graduation's "Type" unselected
 3. Attempt to proceed
 4. Verify a validation message appears for Type</t>
@@ -1555,7 +1555,7 @@
     <t>Verifying that leaving Graduation's % Of Marks blank is rejected when attempting to proceed</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Leave Graduation's "% Of Marks" blank
 3. Attempt to proceed
 4. Verify a validation message appears for % Of Marks</t>
@@ -1576,7 +1576,7 @@
     <t>Verifying that leaving Graduation's Specialization blank does NOT block proceeding, since it is the one optional field in an otherwise-mandatory section</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill Graduation's Course, From, To, Type, % Of Marks with valid data, leaving Specialization blank
 3. Click Next</t>
   </si>
@@ -1596,7 +1596,7 @@
     <t>Verifying the Course dropdown (Graduation) lists exactly the expected course options, correctly worded and in the expected order. Confirmed complete from user-provided screenshots (2026-09-22) plus the user's explicit confirmation (2026-09-23) that "Master of Labour Studies" and "Master of Veterinary Science" are adjacent with no entries between them - an earlier note about an uncaptured gap there is resolved.</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Click the Graduation "Course" dropdown
 3. Verify the list of options shown</t>
   </si>
@@ -1616,7 +1616,7 @@
     <t>Verifying the Type dropdown (Graduation) lists exactly the expected two options, confirmed from a user-provided screenshot (2026-09-22)</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Click the Graduation "Type" dropdown
 3. Verify the list of options shown</t>
   </si>
@@ -1636,7 +1636,7 @@
     <t>Verifying that a Graduation % Of Marks value below 2 or above 100 is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a Graduation "% Of Marks" value outside [2, 100]
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1657,7 +1657,7 @@
     <t>Verifying that a decimal % Of Marks value within [2, 100] is accepted for Graduation (e.g. 78.00, as shown in the app's own screenshot)</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a valid decimal value (e.g. "78.00") into Graduation's "% Of Marks"
 3. Verify it is accepted</t>
   </si>
@@ -1677,7 +1677,7 @@
     <t>Verifying that a Graduation "To" date earlier than or equal to "From" is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a Graduation "From" date, and a "To" date earlier than or equal to it
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1698,7 +1698,7 @@
     <t>Verifying that a Graduation "To" date set in the future is rejected (Graduation's "From" CAN legitimately be in the future for an ongoing degree - only "To" is checked here)</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter a future date into Graduation's "To"
 3. Attempt to proceed
 4. Verify a validation message appears</t>
@@ -1719,7 +1719,7 @@
     <t>Verifying that when 12th is filled, Graduation's "From" date being earlier than or equal to 12th's "To" date is rejected as chronologically inconsistent</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill 12th with a valid From/To range
 3. Fill Graduation's "From" date with a date earlier than or equal to 12th's "To" date
 4. Attempt to proceed
@@ -1741,7 +1741,7 @@
     <t>Verifying that clicking "+ Add Qualification" reveals a new "Additional Qualification" block with the same fields as Graduation (Course*, From*, To*, Type*, Specialization, % Of Marks*) and the same mandatory pattern</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Click "+ Add Qualification"
 3. Verify an "Additional Qualification" block appears with Course*, From*, To*, Type*, Specialization, % Of Marks* fields</t>
   </si>
@@ -1764,7 +1764,7 @@
     <t>Edge Case</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill the Graduation block validly
 3. Click "+ Add Qualification", fill the new block validly, and repeat well past the previously-assumed limit of 10 total blocks
 4. Verify each addition succeeds and the button remains enabled throughout</t>
@@ -1785,7 +1785,7 @@
     <t>Verifying an Additional Qualification block can be individually removed (a delete/trash icon was visible on the block in the user-provided screenshot)</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Click "+ Add Qualification" to add a block
 3. Click the delete/trash icon on that block
 4. Verify the block is removed</t>
@@ -1806,7 +1806,7 @@
     <t>Verifying that removing a qualification block does not leave the section in a state where nothing further can be added. NOTE ON HISTORY: this row originally read 'removing a block re-enables + Add Qualification if it was disabled at the cap'. That premise became moot when the user ruled on 2026-09-24 that no cap should exist (see TC_80), so the row was rewritten to cover the part still worth testing rather than being retired. Distinct from TC_81, which only proves a block CAN be removed; this covers what the section can still do afterwards.</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill Graduation validly, then add and fill two additional qualification blocks (3 total)
 3. Remove the last additional block via its delete icon, accepting the confirmation dialog
 4. Verify the block count drops to 2 and "+ Add Qualification" is still enabled
@@ -1829,7 +1829,7 @@
     <t>Verifying that leaving one Additional Qualification block's Course blank is rejected on its own, separately from Graduation's own Course field</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill Graduation with valid data
 3. Click "+ Add Qualification" and leave that block's "Course" blank while filling its other fields validly
 4. Attempt to proceed
@@ -1854,7 +1854,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter "&lt;script&gt;alert(1)&lt;/script&gt;" into 10th's Specialization field
 3. Proceed/save as normal
 4. Verify no JavaScript dialog/alert appears and the payload is treated as plain text, not executed</t>
@@ -1875,7 +1875,7 @@
     <t>Verifying that a SQL-injection-style payload entered into Graduation's Specialization field does not cause unexpected behavior</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Enter "' OR '1'='1" into Graduation's Specialization field
 3. Proceed/save as normal
 4. Verify the app behaves normally - no error page, no unexpected data exposure</t>
@@ -1896,7 +1896,7 @@
     <t>Verifying that data entered into Qualification Details and saved via Save is retained after a page refresh. Worth checking against the same real bug already confirmed on Personal Details (TC_39: Save throws "Executing runtime operation failed for security reasons") - may be the same underlying defect, or may be section-specific; needs its own live confirmation rather than assuming either way.</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill in valid data across 10th, 12th, and Graduation
 3. Click "Save"
 4. Refresh the page
@@ -1918,7 +1918,7 @@
     <t>Verifying that Experience Details actually becomes reachable once Graduation's mandatory fields are validly filled (10th/12th can remain blank, since optional) and Next is clicked</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill Graduation's mandatory fields with valid data (10th/12th left blank)
 3. Click "Next"
 4. Verify the "3. Experience Details" section renders</t>
@@ -1942,7 +1942,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details/General Details complete, Qualification Details left incomplete (Graduation not validly filled)</t>
   </si>
   <si>
-    <t>1. Complete Personal Details/General Details, reach Qualification Details, leave Graduation incomplete
+    <t xml:space="preserve">1. Complete Personal Details/General Details, reach Qualification Details, leave Graduation incomplete
 2. Attempt to click "3. Experience Details" in the step indicator
 3. Verify the step does not open</t>
   </si>
@@ -1965,7 +1965,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details and Qualification Details both validly completed, currently on Qualification Details or later</t>
   </si>
   <si>
-    <t>1. Complete Personal Details and Qualification Details, reaching Experience Details (or staying on Qualification Details)
+    <t xml:space="preserve">1. Complete Personal Details and Qualification Details, reaching Experience Details (or staying on Qualification Details)
 2. Click the "1. Personal Details" step circle
 3. Verify the Personal Details section renders</t>
   </si>
@@ -1988,7 +1988,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details and Qualification Details both validly completed, Experience Details NOT yet completed, currently navigated back to Personal Details</t>
   </si>
   <si>
-    <t>1. Complete Personal Details and Qualification Details (do not complete Experience Details)
+    <t xml:space="preserve">1. Complete Personal Details and Qualification Details (do not complete Experience Details)
 2. Navigate back to Personal Details via its step circle
 3. Click the "2. Qualification Details" step circle - verify it opens directly
 4. Click the "3. Experience Details" step circle - verify it does NOT open, since Experience Details has not yet been completed</t>
@@ -2012,7 +2012,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details and Qualification Details both validly completed with known field values</t>
   </si>
   <si>
-    <t>1. Complete Personal Details and Qualification Details with known valid data
+    <t xml:space="preserve">1. Complete Personal Details and Qualification Details with known valid data
 2. Navigate back to Personal Details via its step circle and change one field (e.g. First Name), then save/proceed
 3. Navigate forward to Qualification Details via its step circle
 4. Verify Qualification Details' previously-entered data (10th/12th/Graduation fields) is still intact, unchanged</t>
@@ -2036,7 +2036,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details and Qualification Details fully and validly completed</t>
   </si>
   <si>
-    <t>1. Complete Personal Details and Qualification Details (Graduation) with valid data
+    <t xml:space="preserve">1. Complete Personal Details and Qualification Details (Graduation) with valid data
 2. Click "Next"
 3. Verify the step indicator shows "3. Experience Details" as the current step
 4. Verify the "3.1 Work Experience" section is visible</t>
@@ -2057,7 +2057,7 @@
     <t>Verifying the section heading, the "Are you experienced?" question, field labels, buttons, and the confirmation checkbox text are present and correctly worded</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Verify the heading "3.1 Work Experience"
 3. Verify the question "Are you experienced ?*" with "Yes"/"No" radio options
 4. Verify field labels: "Company*", "Annual Package*", "Designation*", "H.Q.*", "Currently working here ?*", "From*", "To*", "Reason of Leaving*"
@@ -2081,7 +2081,7 @@
     <t>Verifying step 1 and step 2 both show a checkmark (completed), and step 3 (Experience Details) shows as the current/active step</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Verify the visual state of all 3 step-indicator items</t>
   </si>
   <si>
@@ -2100,7 +2100,7 @@
     <t>Verifying that clicking the +/- toggle on the "3.1 Work Experience" section header correctly collapses and expands that section's fields, matching the toggle pattern used elsewhere in Phase 1</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Click the toggle to collapse the section; verify fields hidden and icon changes to "+"
 3. Click the toggle again to expand; verify fields reappear and icon changes to "-"</t>
   </si>
@@ -2120,7 +2120,7 @@
     <t>Verifying that selecting "No" removes the Company/Annual Package/Designation/H.Q./dates/Reason of Leaving fields entirely, and Submit only requires the confirmation checkbox to be checked</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Select "No" for "Are you experienced?"
 3. Verify the Company/experience-detail fields are not shown
 4. Check the confirmation checkbox and click Submit</t>
@@ -2141,7 +2141,7 @@
     <t>Verifying that selecting "Yes" reveals the Company, Annual Package, Designation, H.Q., Currently working here?, From, To, and Reason of Leaving fields</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Select "Yes" for "Are you experienced?"
 3. Verify all experience-detail fields become visible</t>
   </si>
@@ -2161,7 +2161,7 @@
     <t>Verifying that leaving Company blank (with "Are you experienced?" = Yes) is rejected when attempting to submit</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Leave "Company" blank, fill the rest validly
 3. Attempt to Submit
 4. Verify a validation message appears for Company</t>
@@ -2182,7 +2182,7 @@
     <t>Verifying that leaving Annual Package blank is rejected when attempting to submit</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Leave "Annual Package" blank, fill the rest validly
 3. Attempt to Submit
 4. Verify a validation message appears for Annual Package</t>
@@ -2203,7 +2203,7 @@
     <t>Verifying that leaving Designation blank is rejected when attempting to submit</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Leave "Designation" blank, fill the rest validly
 3. Attempt to Submit
 4. Verify a validation message appears for Designation</t>
@@ -2224,7 +2224,7 @@
     <t>Verifying that leaving H.Q. blank is rejected when attempting to submit</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Leave "H.Q." blank, fill the rest validly
 3. Attempt to Submit
 4. Verify a validation message appears for H.Q.</t>
@@ -2245,7 +2245,7 @@
     <t>Verifying that leaving "From" blank is rejected when attempting to submit, with "Currently working here ?" left UNCHECKED (the common case - a past employer, by definition, is not currently worked at). CONDITIONAL BEHAVIOUR, confirmed live 2026-09-24: this same check on the CHECKED branch ("Currently working here ?" ticked) works correctly and is NOT covered by this row - a blank "From" there is properly rejected with "Please enter From date", no error. Only the unchecked branch is broken.</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Leave "Currently working here ?" UNCHECKED
 3. Leave "From" blank, fill every other field validly
 4. Attempt to Submit
@@ -2255,7 +2255,7 @@
     <t>"From" should be rejected with a mandatory-field validation message ("Please enter From date", matching the wording already confirmed on the checked branch) when left blank and "Currently working here ?" is unchecked - not a runtime/server error.</t>
   </si>
   <si>
-    <t>FAILED - and note the PRECISE shape, which is narrower than an earlier reading of this row claimed. The "From" mandatory-field rule is CONDITIONAL on the "Currently working here ?" checkbox. Probed live 2026-09-24 on two brand-new accounts, one per branch, every other mandatory field validly filled and the submission never confirmed:
+    <t xml:space="preserve">FAILED - and note the PRECISE shape, which is narrower than an earlier reading of this row claimed. The "From" mandatory-field rule is CONDITIONAL on the "Currently working here ?" checkbox. Probed live 2026-09-24 on two brand-new accounts, one per branch, every other mandatory field validly filled and the submission never confirmed:
   - Checkbox CHECKED: a blank "From" is correctly rejected with "Please enter From date". No runtime error. (Independently confirmed by the user's own screenshot the same day.)
   - Checkbox UNCHECKED: a blank "From" produces NO validation message at all - instead the app throws "An error occurred, please contact your system administrator." with the server returning HTTP 560 from /xas/.
 So the validation rule EXISTS but is only wired into the currently-working branch; the not-currently-working path lets the null reach the submit logic and fail server-side. Reproduced across 3 consecutive automated runs plus the dedicated two-branch probe, and also on a brand-new never-touched experience block, so it is not an artefact of how the automation clears the field. Sibling "To" validates cleanly in both branches ("Please enter To date").
@@ -2274,7 +2274,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details and Qualification Details fully and validly completed | "Currently working here?" left unchecked</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes", leave "Currently working here?" unchecked
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes", leave "Currently working here?" unchecked
 2. Leave "To" blank, fill the rest validly
 3. Attempt to Submit
 4. Verify a validation message appears for To</t>
@@ -2295,7 +2295,7 @@
     <t>Verifying that leaving "Reason of Leaving" blank (with "Currently working here?" unchecked) is rejected when attempting to submit</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes", leave "Currently working here?" unchecked
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes", leave "Currently working here?" unchecked
 2. Leave "Reason of Leaving" blank, fill the rest validly
 3. Attempt to Submit
 4. Verify a validation message appears for Reason of Leaving</t>
@@ -2316,7 +2316,7 @@
     <t>Verifying that checking "Currently working here?" disables/greys out the "To" date field, since a current job has no end date</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Check "Currently working here?"
 3. Attempt to click into / edit the "To" field</t>
   </si>
@@ -2336,7 +2336,7 @@
     <t>Verifying that 'Currently working here?' governs ONLY the 'To' date, and that 'Reason of Leaving' is independent of it - staying enabled and mandatory regardless. NOTE ON HISTORY: this row originally asserted the opposite, that 'Reason of Leaving' should also be disabled when the checkbox is ticked, and was recorded as a confirmed defect (Failed, P2) on that basis. The user reversed that ruling on 2026-09-24 with a screenshot showing the two fields are not related. The expectation below and the automation were rewritten to match, and the defect is withdrawn.</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section (3.1 Work Experience)
+    <t xml:space="preserve">1. Reach the Experience Details section (3.1 Work Experience)
 2. Select "Yes" for "Are you experienced ?"
 3. Check "Currently working here ?"
 4. Verify the "To" date field becomes disabled
@@ -2358,7 +2358,7 @@
     <t>Verifying that unchecking "Currently working here?" after it was checked re-enables the "To" date field for input</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Check "Currently working here?", then uncheck it
 3. Attempt to click into / edit the "To" field</t>
   </si>
@@ -2378,7 +2378,7 @@
     <t>Verifying that a "To" date earlier than or equal to "From" is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Enter a "From" date, and a "To" date earlier than or equal to it
 3. Attempt to Submit
 4. Verify a validation message appears</t>
@@ -2399,7 +2399,7 @@
     <t>Verifying that a future "From" or "To" date is rejected</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Enter a future date into "From" or "To"
 3. Attempt to Submit
 4. Verify a validation message appears</t>
@@ -2420,7 +2420,7 @@
     <t>Verifying that clicking "+ Add Experience" reveals a new experience entry block with the same fields and mandatory pattern as the first (Company*, Annual Package*, Designation*, H.Q.*, Currently working here?*, From*, To*, Reason of Leaving*)</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Click "+ Add Experience"
 3. Verify a new experience block appears with the same fields</t>
   </si>
@@ -2440,7 +2440,7 @@
     <t>Verifying the delete/trash icon visible on an experience block (per the user-provided screenshot) removes only that specific block</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Click "+ Add Experience" to add a second block
 3. Click the delete/trash icon on one block
 4. Verify only that block is removed, the other remains intact</t>
@@ -2461,7 +2461,7 @@
     <t>Verifying whether "+ Add Experience" has a maximum, mirroring Qualification Details' confirmed 9-additional/10-total cap on "+ Add Qualification". NOT yet confirmed for Experience - needs a live probe once the current environment/Chrome-block issue clears; not guessed here.</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Click "+ Add Experience" repeatedly
 3. Observe whether the button becomes disabled after some maximum count</t>
   </si>
@@ -2481,7 +2481,7 @@
     <t>Verifying that Submit is blocked when the "I confirm that the details provided..." checkbox is left unchecked, regardless of whether "Are you experienced?" is Yes or No</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Fill all required fields validly (or select "No")
 3. Leave the confirmation checkbox unchecked
 4. Attempt to Submit
@@ -2503,7 +2503,7 @@
     <t>Verifying that Submit does not succeed while any mandatory Experience field (with "Are you experienced?" = Yes) is left incomplete, even if the confirmation checkbox is checked</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Leave one or more mandatory fields incomplete
 3. Check the confirmation checkbox and attempt to Submit
 4. Verify Submit is blocked with a validation message</t>
@@ -2524,7 +2524,7 @@
     <t>Verifying that a script-injection payload entered into Company does not execute, matching the same security-check pattern used elsewhere in this project (e.g. Sign In's Username field)</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes"
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes"
 2. Enter "&lt;script&gt;alert(1)&lt;/script&gt;" into "Company"
 3. Proceed/submit as normal
 4. Verify no JavaScript dialog/alert appears and the payload is treated as plain text</t>
@@ -2545,7 +2545,7 @@
     <t>Verifying that a SQL-injection-style payload entered into Reason of Leaving does not cause unexpected behavior</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section, select "Yes", leave "Currently working here?" unchecked
+    <t xml:space="preserve">1. Reach the Experience Details section, select "Yes", leave "Currently working here?" unchecked
 2. Enter "' OR '1'='1" into "Reason of Leaving"
 3. Proceed/submit as normal
 4. Verify the app behaves normally - no error page, no unexpected data exposure</t>
@@ -2563,7 +2563,7 @@
     <t>Verifying that submitting Experience Details with all mandatory fields validly filled and the confirmation checkbox checked transitions the candidate into Phase 2. This test only verifies the Phase 1-to-Phase 2 TRANSITION itself (a Phase 1 boundary behavior) - it does not exercise Phase 2's own content/functionality, which remains out of scope while Phase 2 work is deferred.</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Fill all mandatory fields validly (or select "No")
 3. Check the confirmation checkbox
 4. Click "Submit"
@@ -2585,7 +2585,7 @@
     <t>Verifying that data entered into Experience Details and saved via Save is retained after a page refresh. Worth checking against the same real bug already confirmed on Personal Details (TC_39: Save throws "Executing runtime operation failed for security reasons") - may be the same underlying defect or may be section-specific; needs its own live confirmation.</t>
   </si>
   <si>
-    <t>1. Reach the Experience Details section
+    <t xml:space="preserve">1. Reach the Experience Details section
 2. Fill in valid experience data
 3. Click "Save"
 4. Refresh the page
@@ -2610,7 +2610,7 @@
     <t>Reached via an authenticated candidate session (Sign Up or Sign In) - Email ID, Aadhaar Number, and Division are auto-populated from that account and cannot be edited on this page | Personal Details and General Details fully and validly completed</t>
   </si>
   <si>
-    <t>1. Reach the Qualification Details section
+    <t xml:space="preserve">1. Reach the Qualification Details section
 2. Fill 10th with a valid range ending in a given year (e.g. 02/02/2018 - 02/02/2019)
 3. Fill 12th so it completes LESS than 2 years after 10th's "To" date (e.g. 02/02/2019 - 02/02/2020, only a 1-year gap)
 4. Keep Graduation's dates well clear of 12th's range so Graduation's own chronological rule cannot mask this one
@@ -2623,18 +2623,1740 @@
   <si>
     <t>FAILED - confirmed live 2026-09-23 across 2 consecutive clean runs (identical result both times, no flakiness). With 10th filled 02/02/2018-02/02/2019 and 12th filled 02/02/2019-02/02/2020 - a gap of only ONE year between 10th completing and 12th completing, which skips the 11th year entirely - Next was ACCEPTED with ZERO validation messages and the form advanced straight to the Experience Details section (confirmed from the failure screenshot: steps 1 and 2 checkmarked, "3.1 Work Experience" rendered). No minimum-duration rule between 10th and 12th exists. Graduation was kept well clear at 2022-2024 and all dates were in the past, so no other rule could have masked this. Related but distinct from TC_65, which covers start-date ORDERING between 10th and 12th (and which found that rule is keyed off the wrong date field); this case is about the minimum SPAN between the two.</t>
   </si>
+  <si>
+    <t>Verify header, footer, and step indicator on the Application Form - Phase 2 page</t>
+  </si>
+  <si>
+    <t>Verifying the page shell (header logo, account icon, Sign out button, footer, step indicator) is present and correct on reaching Phase 2, mirroring Phase 1's own TC_01 Per the user (2026-09-24), Phase 2's step-indicator navigation follows the same rules already confirmed in Phase 1 (TC_89-91): a completed step can be clicked back to directly, and forward navigation is capped at the highest section ever reached.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 (Personal Details, Qualification Details, Experience Details) - the candidate is auto-navigated into Application Form - Phase 2, section "1. Other Details"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete and submit Phase 1
+2. Verify the header shows "Application Form - Phase 2" with the Mankind logo, account icon, and "Sign out" button
+3. Verify the step indicator shows "1. Other Details" as current and "2. Upload Documents" as not yet reached
+4. Verify the footer is present</t>
+  </si>
+  <si>
+    <t>The header, footer, and step indicator should all be present and correctly reflect Phase 2's own 2-step flow (Other Details, Upload Documents), with step 1 shown as current</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25 (tests/Candidate/Phase2.spec.js, pooled account signed in straight onto Phase 2). Passed on first run. Page title "Mendix - Application Form - Phase 2", header "Application Form - Phase 2" with the Mankind logo, account icon and "Sign out" button all visible. Step indicator shows "1. Other Details" as current (filled dark circle) and "2. Upload Documents" as not yet reached (pale grey circle). Footer shows "© Mankind@2026. All rights reserved." and the Helpline line.</t>
+  </si>
+  <si>
+    <t>Verify all static UI text in the "1.1 Other Details" section</t>
+  </si>
+  <si>
+    <t>Verifying the section heading and all field labels in 1.1 Other Details are present and correctly worded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1. Other Details" section
+2. Verify the sub-heading "1.1 Other Details"
+3. Verify field labels: "Name", "Mobile Number", "Email ID", "PAN Card Number", "Blood Group*", "Religion*", "Marital Status", "Date Of Marriage"</t>
+  </si>
+  <si>
+    <t>The section heading and all field labels should be present and correctly worded, with Blood Group and Religion showing the red mandatory asterisk. Marital Status, being disabled and prefilled from Phase 1 (like Name, Mobile Number, Email ID and PAN Card Number), should NOT show an asterisk, nor should Date Of Marriage.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Confirmed 3 of 3 runs. Present and worded correctly: sub-heading "1.1 Other Details" and the labels "Name", "Mobile Number", "Email ID", "PAN Card Number", "Blood Group", "Religion", "Marital Status", "Date Of Marriage". Blood Group and Religion show the red mandatory asterisk. Name, Mobile Number, Email ID, PAN Card Number, Marital Status and Date Of Marriage show none. User ruling (2026-09-25): Marital Status is disabled/prefilled from Phase 1 and cannot be edited on Phase 2, so it correctly has no asterisk, the same as the other prefilled fields. Not a defect - expected result corrected.</t>
+  </si>
+  <si>
+    <t>Verify Name, Mobile Number, Email ID, PAN Card Number, and Marital Status are read-only and correctly carry over their values from Phase 1</t>
+  </si>
+  <si>
+    <t>Verifying these 5 fields are disabled/non-editable on the Phase 2 page and display the exact values the candidate entered during Phase 1 - confirmed by the user (2026-09-24) that all 5 are fully read-only here, not just pre-filled defaults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the exact Name, Mobile Number, Email ID, PAN Card Number, and Marital Status values entered during this candidate's Phase 1
+2. Reach the "1.1 Other Details" section
+3. Verify all 5 fields display those exact values
+4. Attempt to click into and edit each of the 5 fields</t>
+  </si>
+  <si>
+    <t>All 5 fields should be disabled (not editable) and should display the exact values carried over from this candidate's own Phase 1 submission</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Used the pooled account 907661151274, whose Phase 1 was filled with the standard valid data. All 5 fields carry over that data exactly: Name "Discovery User 18", Mobile Number "9876543210", Email ID "discovery.candidate18@gmail.com", PAN Card Number "ATBPV6191F", Marital Status "Single". All 5 are disabled. Force-clicking and typing into Name/Mobile/Email/PAN left each value unchanged, and force-clicking Marital Status and pressing ArrowDown+Enter left it on "Single".</t>
+  </si>
+  <si>
+    <t>Verify Blood Group is a mandatory field</t>
+  </si>
+  <si>
+    <t>Verifying that leaving Blood Group unselected is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section
+2. Leave "Blood Group" unselected
+3. Attempt to proceed (click Next or Save)
+4. Verify a validation message appears for Blood Group</t>
+  </si>
+  <si>
+    <t>Blood Group should be rejected with a mandatory-field validation message when left unselected</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Religion was set to "Hinduism" and Blood Group reset to its blank option. Clicking Next was rejected with the validation message "Blood group is mandatory". No "Religion is mandatory" message appeared, and the candidate stayed on 1. Other Details.</t>
+  </si>
+  <si>
+    <t>Verify the Blood Group dropdown shows the correct list of options</t>
+  </si>
+  <si>
+    <t>Verifying the Blood Group dropdown lists exactly the expected options, correctly worded. Confirmed from a user-provided screenshot (2026-09-24).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section
+2. Click the "Blood Group" dropdown
+3. Verify the list of options shown</t>
+  </si>
+  <si>
+    <t>The Blood Group dropdown should show exactly these options, in this order: "A+", "A-", "AB+", "AB-", "B+", "B-", "O+", "O-", "Unknown"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Apart from the blank placeholder, the Blood Group dropdown shows exactly these options in this order: "A+", "A-", "AB+", "AB-", "B+", "B-", "O+", "O-", "Unknown".</t>
+  </si>
+  <si>
+    <t>Verify Religion is a mandatory field</t>
+  </si>
+  <si>
+    <t>Verifying that leaving Religion unselected is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section
+2. Leave "Religion" unselected
+3. Attempt to proceed (click Next or Save)
+4. Verify a validation message appears for Religion</t>
+  </si>
+  <si>
+    <t>Religion should be rejected with a mandatory-field validation message when left unselected</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Blood Group was set to "A+" and Religion reset to its blank option. Clicking Next was rejected with the validation message "Religion is mandatory". No "Blood group is mandatory" message appeared, and the candidate stayed on 1. Other Details.</t>
+  </si>
+  <si>
+    <t>Verify the Religion dropdown shows the correct list of options</t>
+  </si>
+  <si>
+    <t>Verifying the Religion dropdown lists exactly the expected options, correctly worded. Confirmed from a user-provided screenshot (2026-09-24).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section
+2. Click the "Religion" dropdown
+3. Verify the list of options shown</t>
+  </si>
+  <si>
+    <t>The Religion dropdown should show exactly these options, in this order: "Hinduism", "Islam", "Christianity", "Sikhism", "Buddhism", "Jainism", "Other"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Apart from the blank placeholder, the Religion dropdown shows exactly these options in this order: "Hinduism", "Islam", "Christianity", "Sikhism", "Buddhism", "Jainism", "Other".</t>
+  </si>
+  <si>
+    <t>Verify Date Of Marriage stays disabled for every Marital Status other than "Married"</t>
+  </si>
+  <si>
+    <t>Verifying Date Of Marriage is enabled ONLY for "Married" - Phase 1's Marital Status dropdown has multiple non-Married options (Single, Divorced, Widowed, Other), and this field should stay disabled for ALL of them, not just one arbitrary "not married" case.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 (Personal Details, Qualification Details, Experience Details) - the candidate is auto-navigated into Application Form - Phase 2, section "1. Other Details" | This candidate's Phase 1 Marital Status was NOT "Married"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section on accounts whose Phase 1 Marital Status is each of "Single", "Divorced", "Widowed", and "Other" in turn
+2. For each, attempt to click into / edit "Date Of Marriage"</t>
+  </si>
+  <si>
+    <t>"Date Of Marriage" should remain disabled and not accept input for every Marital Status other than "Married" - Single, Divorced, Widowed, and Other alike.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed. The first attempt hit a sign-in page load timeout (the login form fill timed out before any assertion ran). That was treated as an infrastructure error and re-run, and the re-run passed. Signed in, in turn, as the 4 dedicated accounts whose Phase 1 Marital Status is "Single" (907661151274), "Divorced" (995131365728), "Widowed" (820854323698) and "Other" (594542374973). On each, Phase 2 Marital Status showed that exact value and Date Of Marriage was disabled. Force-clicking it and typing "15/02/2020" left it empty every time.</t>
+  </si>
+  <si>
+    <t>Verify Date Of Marriage becomes enabled ONLY when Marital Status (from Phase 1) is "Married"</t>
+  </si>
+  <si>
+    <t>Verifying that for a candidate whose Phase 1 Marital Status was "Married", the Date Of Marriage field on Phase 2 is enabled and accepts input. NEEDS a dedicated Phase 1 test candidate who selected "Married" - none of this project's existing pooled/fixture candidates have done so yet.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 (Personal Details, Qualification Details, Experience Details) - the candidate is auto-navigated into Application Form - Phase 2, section "1. Other Details" | This candidate's Phase 1 Marital Status was "Married"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section on an account whose Phase 1 Marital Status is "Married"
+2. Verify "Date Of Marriage" is enabled
+3. Enter a valid date and verify it is accepted</t>
+  </si>
+  <si>
+    <t>"Date Of Marriage" should be enabled and accept a valid date when the candidate's Phase 1 Marital Status is "Married"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Used the dedicated account 574030372966, whose Phase 1 Marital Status is "Married". On Phase 2, Marital Status shows "Married" and Date Of Marriage is enabled. Entering "15/02/2020" and tabbing out kept the value "15/02/2020", with no date/marriage validation message.</t>
+  </si>
+  <si>
+    <t>Verify Date Of Marriage is optional even when enabled</t>
+  </si>
+  <si>
+    <t>Verifying that leaving Date Of Marriage blank (on a Married candidate, where it is enabled) does not block proceeding - confirmed by the user (2026-09-24) that it carries no mandatory asterisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section on an account whose Phase 1 Marital Status is "Married"
+2. Leave "Date Of Marriage" blank, fill Blood Group and Religion validly
+3. Attempt to proceed (click Next or Save)</t>
+  </si>
+  <si>
+    <t>Leaving "Date Of Marriage" blank should NOT block proceeding, even though it is enabled, since it is not a mandatory field</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Failed on 3 of 3 runs, same result each time. Used the dedicated "Married" account 574030372966: Date Of Marriage left blank (enabled, no asterisk shown), Blood Group "A+", Religion "Hinduism", then Next clicked. The app raised "Date Of Marriage is mandatory", so a blank Date Of Marriage DOES block proceeding for a Married candidate. It is enforced as mandatory even though the label has no asterisk. Full message list after Next: "Date Of Marriage is mandatory", "Date of Birth is mandatory", "Please select whether you were a PF member in your previous establishment.", "UAN Number is mandatory", "Name is mandatory", "Relation is mandatory", "Contact Number is mandatory". The other messages come from the Dependent/UAN/Emergency Contact sections, which were deliberately left blank so this pooled account is never advanced. No Blood Group or Religion message appeared.</t>
+  </si>
+  <si>
+    <t>Verify Date Of Marriage does not accept a future date</t>
+  </si>
+  <si>
+    <t>Verifying that a future Date Of Marriage is rejected, on a Married candidate where the field is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section on an account whose Phase 1 Marital Status is "Married"
+2. Enter a future date into "Date Of Marriage"
+3. Attempt to proceed
+4. Verify a validation message appears</t>
+  </si>
+  <si>
+    <t>A future "Date Of Marriage" should be rejected with a validation message</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Used the dedicated "Married" account 574030372966. Entered the future date "25/03/2027" (today + 6 months) into Date Of Marriage, filled Blood Group/Religion, then clicked Next. It was rejected with the validation message "Date Of Marriage should be less than today", shown on the Date Of Marriage field itself.</t>
+  </si>
+  <si>
+    <t>Verify the "1.1 Other Details" section toggle expands and collapses correctly</t>
+  </si>
+  <si>
+    <t>Verifying that clicking the +/- toggle on the "1.1 Other Details" section header correctly collapses and expands that section's fields, matching the toggle pattern used throughout Phase 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.1 Other Details" section
+2. Click the toggle to collapse the section; verify fields hidden and icon changes to "+"
+3. Click the toggle again to expand; verify fields reappear and icon changes to "-"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The "1.1 Other Details" header icon starts as "-" (expanded). Clicking it hid the section's fields (Name, Blood Group etc.) and the icon changed to "+". Clicking it again brought the fields back and the icon returned to "-".</t>
+  </si>
+  <si>
+    <t>Verify all static UI text in the "1.2 Dependent Details" section</t>
+  </si>
+  <si>
+    <t>Verifying the section heading and all field labels in 1.2 Dependent Details are present and correctly worded</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 - the candidate is on Application Form - Phase 2, section "1. Other Details"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Verify the sub-heading "1.2 Dependent Details"
+3. Verify field labels: "Name*", "Relation*", "Date of Birth*", "Date of Demise (if applicable)", "Nominee*"
+4. Verify the "Add Member" button</t>
+  </si>
+  <si>
+    <t>The section heading, all field labels (with mandatory fields showing a red asterisk - Name, Relation, Date of Birth, Nominee; Date of Demise unmarked), and the "Add Member" button should all be present and correctly worded</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Section heading "1.2 Dependent Details" is present. Column labels "Name", "Relation", "Date of Birth", "Date of Demise (if applicable)" and "Nominee" are present and correctly worded. Name, Relation, Date of Birth and Nominee show the red asterisk; Date of Demise shows none. The add button is present and its live text is "Add Member". There is no literal "+" in the text or via an icon, so the "+" in "+ Add Member" was read as notation, the same way Phase 1 treats "+ Add Qualification".</t>
+  </si>
+  <si>
+    <t>Verify the "1.2 Dependent Details" section toggle expands and collapses correctly</t>
+  </si>
+  <si>
+    <t>Verifying that clicking the +/- toggle on the "1.2 Dependent Details" section header correctly collapses and expands that section's fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Click the toggle to collapse the section; verify fields hidden and icon changes to "+"
+3. Click the toggle again to expand; verify fields reappear and icon changes to "-"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The "1.2 Dependent Details" header icon starts as "-" (expanded). Clicking it hid the dependent rows and the "Add Member" button, and the icon changed to "+". Clicking it again brought both back and the icon returned to "-".</t>
+  </si>
+  <si>
+    <t>Verify Father and Mother rows exist by default in Dependent Details</t>
+  </si>
+  <si>
+    <t>Verifying that reaching Dependent Details for the first time already shows two dependent rows, with Relation pre-set to "Father" and "Mother" respectively (Name carried over from Phase 1; Date of Birth still blank, to be filled by the candidate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section on a candidate who has not yet filled this section
+2. Verify exactly two dependent rows already exist
+3. Verify the first row's Relation reads "Father" and the second row's Relation reads "Mother"</t>
+  </si>
+  <si>
+    <t>Two dependent rows should exist by default, with Relation pre-set to "Father" (row 1) and "Mother" (row 2)</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Exactly two dependent rows exist by default. Row 1 Relation is "Father" and row 2 Relation is "Mother", and both Relation dropdowns are disabled. Note: this row's description says Name/Date of Birth start blank. Live, Date of Birth is blank, but Name is already prefilled from the candidate's Phase 1 parent details ("Amandeep Singh" / "Kashish Kaur"). The Expected Result itself (two rows, Father then Mother) is met.</t>
+  </si>
+  <si>
+    <t>Verify the delete icon is disabled or hidden for the Father and Mother rows</t>
+  </si>
+  <si>
+    <t>Verifying the Father and Mother rows cannot be removed - confirmed by the user (2026-09-24) that their trash icon is disabled/hidden, unlike rows added via "+ Add Member"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Locate the delete/trash icon for the Father row and the Mother row
+3. Verify each is disabled or not present, and attempting to click it (if present) does not remove the row</t>
+  </si>
+  <si>
+    <t>The Father and Mother rows' delete/trash icon should be disabled or hidden - neither row can be removed from the UI</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The Father and Mother rows each show a greyed-out trash icon marked disabled. It is a plain, non-clickable image, unlike the clickable trash icon that rows added via "Add Member" get. Force-clicking each one opened no delete confirmation, both rows remained (still exactly 2, Father and Mother), and no row had a clickable delete icon.</t>
+  </si>
+  <si>
+    <t>Verify Name is a mandatory field for a dependent</t>
+  </si>
+  <si>
+    <t>Verifying that leaving a dependent's Name blank is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Leave the Father row's "Name" blank, fill Relation and Date of Birth validly
+3. Attempt to proceed (click Next or Save)
+4. Verify a validation message appears for Name</t>
+  </si>
+  <si>
+    <t>Name should be rejected with a mandatory-field validation message when left blank</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Father row: the prefilled Name was cleared (Relation is preset to "Father" and disabled) and Date of Birth set to "15/08/1965", then Next clicked. The Father Name field showed the validation message "Name is mandatory", and the Date of Birth field had no message. The message was checked on the dependent Name field itself, because Emergency Contact raises an identically worded "Name is mandatory". The cleared Name did not persist: the next sign-in still showed "Amandeep Singh".</t>
+  </si>
+  <si>
+    <t>Verify Relation is a mandatory field for a dependent</t>
+  </si>
+  <si>
+    <t>Verifying that leaving a dependent's Relation unselected is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Click "+ Add Member" to add a new row, leave its "Relation" unselected, fill Name and Date of Birth validly
+3. Attempt to proceed
+4. Verify a validation message appears for Relation</t>
+  </si>
+  <si>
+    <t>Relation should be rejected with a mandatory-field validation message when left unselected</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed. "Add Member" added a third row. It was filled with Name "Test Dependent" and Date of Birth "15/08/2000", its Relation left unselected, and Next clicked. That row's Relation field showed the validation message "Relation is mandatory", and its Name/Date of Birth fields had no message. The first attempt's checks also all passed, but the run errored in our own cleanup step: the "Please complete all mandatory fields (including Nominee, if not already selected) to proceed" dialog was still open and blocked the delete click. The cleanup was fixed and the re-run passed. Note: "Add Member" saves the new row immediately and it survives sign-out, so the test deletes it again afterwards. Verified that the account is back to only Father + Mother.</t>
+  </si>
+  <si>
+    <t>Verify Date of Birth is a mandatory field for a dependent</t>
+  </si>
+  <si>
+    <t>Verifying that leaving a dependent's Date of Birth blank is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Leave the Mother row's "Date of Birth" blank, fill Name and Relation validly
+3. Attempt to proceed
+4. Verify a validation message appears for Date of Birth</t>
+  </si>
+  <si>
+    <t>Date of Birth should be rejected with a mandatory-field validation message when left blank</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The Father row's Date of Birth was set to "15/08/1965". The Mother row's Date of Birth was left blank, with her Name ("Kashish Kaur", prefilled) and Relation ("Mother", preset) in place. Clicking Next gave the validation message "Date of Birth is mandatory" on the Mother row's Date of Birth field, and none on the Father's.</t>
+  </si>
+  <si>
+    <t>Verify Date of Demise (if applicable) is optional</t>
+  </si>
+  <si>
+    <t>Verifying that leaving Date of Demise blank does not block proceeding, since it carries no mandatory asterisk and most dependents are expected to be living</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Fill Name, Relation, and Date of Birth validly for the Father and Mother rows, leaving "Date of Demise" blank on both
+3. Attempt to proceed</t>
+  </si>
+  <si>
+    <t>Leaving "Date of Demise" blank should NOT block proceeding</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Father/Mother rows filled validly: Names prefilled, Relations preset, Date of Birth "15/08/1965" / "15/08/1970", Father ticked as Nominee. Date of Demise was left blank on both rows, then Next clicked. The 1.2 Dependent Details section raised no validation message at all, so a blank Date of Demise does not block this section. The remaining messages came only from the other sections, which were left blank on purpose so this pooled account is never advanced: Blood group, Religion, PF member, UAN Number, and the Emergency Contact Name/Relation/Contact Number.</t>
+  </si>
+  <si>
+    <t>Verify the Relation dropdown shows the correct list of options</t>
+  </si>
+  <si>
+    <t>Verifying the Relation dropdown lists exactly the expected options, correctly worded. Confirmed from a user-provided screenshot (2026-09-24).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Click "+ Add Member" to add a new row (so Relation is freely selectable, not pre-set)
+3. Click that row's "Relation" dropdown
+4. Verify the list of options shown</t>
+  </si>
+  <si>
+    <t>The Relation dropdown should show exactly these options, in this order: "Father", "Mother", "Brother", "Sister", "Spouse", "Grand Father", "Grand Mother", "Father-In-Law", "Mother-In-Law", "Son", "Daughter", "Divorced Spouse", "Guardian"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. After "Add Member" added a third row, its Relation dropdown was enabled and listed exactly, in order: "Father", "Mother", "Brother", "Sister", "Spouse", "Grand Father", "Grand Mother", "Father-In-Law", "Mother-In-Law", "Son", "Daughter", "Divorced Spouse", "Guardian". The test deletes the added row again afterwards.</t>
+  </si>
+  <si>
+    <t>Verify Date of Birth cannot be set in the future</t>
+  </si>
+  <si>
+    <t>Verifying that a future Date of Birth for a dependent is rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Enter a future date into a dependent's "Date of Birth"
+3. Attempt to proceed
+4. Verify a validation message appears</t>
+  </si>
+  <si>
+    <t>A future Date of Birth should be rejected with a validation message</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The Father row's Date of Birth was set to a date 6 months in the future (25/03/2027). The Mother row got a valid Date of Birth (15/08/1970) and was ticked as Nominee. Clicking Next gave the validation message "Date of Birth should be less than today" on the Father row's Date of Birth field, and none on the Mother's.</t>
+  </si>
+  <si>
+    <t>Verify Date of Demise, if filled, must be after Date of Birth</t>
+  </si>
+  <si>
+    <t>Verifying that a Date of Demise earlier than or equal to the dependent's own Date of Birth is rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Enter a Date of Birth, then a Date of Demise earlier than or equal to it
+3. Attempt to proceed
+4. Verify a validation message appears</t>
+  </si>
+  <si>
+    <t>A Date of Demise that is not strictly after Date of Birth should be rejected with a validation message</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Father row: Date of Birth "15/08/1965". Both cases were checked: Date of Demise "15/08/1960" (earlier) and "15/08/1965" (the same day). Each time the Date of Demise field showed "Date of Death should be greater than Date of Birth". The message appears as soon as you leave the field and is still there after Next. Mother was the Nominee, so the deceased-nominee rule could not affect this check.</t>
+  </si>
+  <si>
+    <t>Verify Date of Demise cannot be set in the future</t>
+  </si>
+  <si>
+    <t>Verifying that a future Date of Demise is rejected, since a date of death cannot lie in the future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Enter a future date into a dependent's "Date of Demise"
+3. Attempt to proceed
+4. Verify a validation message appears</t>
+  </si>
+  <si>
+    <t>A future Date of Demise should be rejected with a validation message</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Father row: Date of Birth "15/08/1965", Date of Demise 6 months in the future (25/03/2027). Mother was ticked as Nominee. The Date of Demise field showed "Date of Death should be less than today". The message appears as soon as you leave the field and is still there after Next.</t>
+  </si>
+  <si>
+    <t>Verify only one dependent can be marked as Nominee at a time</t>
+  </si>
+  <si>
+    <t>Verifying that checking a second row's Nominee box automatically unchecks whichever row was previously marked, so at most one Nominee is ever checked. Once a Nominee is chosen it cannot be unticked by clicking it again - the only way to change it is to tick a different row. Confirmed by the user (2026-09-24): auto-uncheck behavior, not a blocking error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section with at least 2 rows present
+2. Check the Father row's "Nominee" box - verify it becomes checked
+3. Check the Mother row's "Nominee" box
+4. Verify the Father row's "Nominee" box is now automatically unchecked, and only the Mother row's remains checked</t>
+  </si>
+  <si>
+    <t>Checking a new row's Nominee box should automatically uncheck the previously-marked row's Nominee box, so only one dependent is ever marked Nominee at a time</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Both Nominee boxes started unchecked. Ticking Father made it [Father checked, Mother unchecked]. Ticking Mother then unticked Father automatically, giving [Father unchecked, Mother checked]. No dialog or error appeared. Also seen while exploring: clicking a ticked Nominee box again does not untick it, so once a Nominee is chosen the count cannot go back to zero.</t>
+  </si>
+  <si>
+    <t>Verify at least one dependent must be marked as Nominee before proceeding</t>
+  </si>
+  <si>
+    <t>Verifying that Submit/Next is blocked if no dependent has been marked as Nominee, matching the mandatory asterisk on "Nominee*"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Fill Name/Relation/Date of Birth validly for the Father and Mother rows, leaving every "Nominee" checkbox unchecked
+3. Attempt to proceed
+4. Verify the page stays on Other Details and the "Information" popup appears: "Please complete all mandatory fields (including Nominee, if not already selected) to proceed"</t>
+  </si>
+  <si>
+    <t>Proceeding without any dependent marked as Nominee should be rejected: the page should stay on Other Details and the "Information" popup should appear with "Please complete all mandatory fields (including Nominee, if not already selected) to proceed"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Father/Mother rows filled validly (Names prefilled, Relations preset, Date of Birth "15/08/1965" / "15/08/1970") with no Nominee ticked, then Next clicked. The page stayed on Other Details and the "Information" popup appeared: "Please complete all mandatory fields (including Nominee, if not already selected) to proceed". No inline message appears on the Nominee column itself. Control check: after ticking Father as Nominee, the same Next did NOT show the popup, although the other sections were still blank. So the popup is the rejection for a missing Nominee.</t>
+  </si>
+  <si>
+    <t>Verify Submit is blocked if the Nominee-marked dependent also has a Date of Demise filled in</t>
+  </si>
+  <si>
+    <t>Verifying that a deceased dependent (Date of Demise filled) cannot be the Nominee. Confirmed by the user (2026-09-24): this is enforced at Submit time with a validation error, NOT by disabling the Nominee checkbox for that row - so the checkbox itself remains checkable even on a row with a Date of Demise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Fill a dependent's "Date of Demise"
+3. Check that same row's "Nominee" box (verify this is NOT blocked at the checkbox itself)
+4. Attempt to proceed
+5. Verify a validation message appears rejecting the submission</t>
+  </si>
+  <si>
+    <t>The Nominee checkbox should remain checkable even on a row with a Date of Demise filled in, but attempting to proceed with that combination should be rejected with a validation message at submit time</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Mother row: Date of Birth "15/08/1970", Date of Demise "15/08/2020". The Mother's Nominee box could still be ticked and stayed ticked, so the checkbox itself does not block it. Clicking Next was rejected with "Relative cannot be nominee as DOD is provided", shown on the Mother row's Date of Demise field. The page stayed on Other Details.</t>
+  </si>
+  <si>
+    <t>Verify "Add Member" adds a new dependent row with the same field requirements</t>
+  </si>
+  <si>
+    <t>Verifying that clicking "Add Member" reveals a new dependent row with the same fields and mandatory pattern as Father/Mother (Name*, Relation*, Date of Birth* required; Date of Demise optional; Nominee available)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Click "Add Member"
+3. Verify a new dependent row appears with Name*, Relation*, Date of Birth*, Date of Demise, and Nominee fields, Relation freely selectable (not pre-set)</t>
+  </si>
+  <si>
+    <t>A new dependent row should appear with the same fields and mandatory pattern as the default Father/Mother rows</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. "Add Member" added a third row: Name blank and editable, Relation blank and freely selectable (not preset or disabled), Date of Birth, Date of Demise and Nominee all enabled, and a working (not greyed-out) delete icon. With Father/Mother filled validly and Father as Nominee, Next was clicked with the new row left blank. The new row showed "Name is mandatory", "Relation is mandatory" and "Date of Birth is mandatory", and no message on its Date of Demise. This is the same mandatory pattern as Father/Mother. The test deletes the added row again afterwards.</t>
+  </si>
+  <si>
+    <t>Verify an added member's delete icon removes that specific row</t>
+  </si>
+  <si>
+    <t>Verifying that a row added via "Add Member" (not Father/Mother) has a working delete/trash icon that removes only that row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Click "Add Member" to add a row, fill it validly
+3. Click that row's delete/trash icon
+4. Verify only that row is removed - Father and Mother rows remain intact</t>
+  </si>
+  <si>
+    <t>Clicking the delete/trash icon on an added member's row should remove only that row, leaving the Father and Mother rows unaffected</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Two members were added and filled: "Member A" / Brother / 15/08/1995 and "Member B" / Sister / 15/08/1998, giving 4 rows. Member A's delete icon was clicked and the "Are you sure you want to delete this?" dialog confirmed with OK. Only Member A's row was removed. Father ("Amandeep Singh"), Mother ("Kashish Kaur") and Member B (Sister, 15/08/1998) were all unchanged, and one deletable row remained. The test deletes Member B afterwards.</t>
+  </si>
+  <si>
+    <t>Verify whether there is a cap on the number of dependent members that can be added</t>
+  </si>
+  <si>
+    <t>Verifying whether "+ Add Member" has a maximum. NOT guessed here - this project has twice recorded a false "cap" defect (Phase 1's Add Qualification and Add Experience) that turned out to be the app correctly refusing to add while an existing block was incomplete, not a real limit. Needs a live check that reads validation messages, not just a count of added rows, before concluding either way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Click "+ Add Member" repeatedly, FILLING each new row validly before adding the next
+3. Observe whether the button ever becomes disabled or blocked after some maximum count</t>
+  </si>
+  <si>
+    <t>To be confirmed live - either the button becomes disabled after a specific maximum, or there is no cap. Do not assume either outcome without a live check that distinguishes a real cap from the app correctly refusing to add an incomplete row.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed. No cap was found. "Add Member" was clicked 13 times, and each new row was filled validly (Name, Relation "Son", Date of Birth "15/08/2010") before the next click. This took the section from 2 rows to 15. Every add worked: the button stayed enabled, and no dialog or validation message appeared. A separate diagnostic run went up to 16 rows the same way. So there is no limit up to at least 16 rows; a higher limit cannot be ruled out. The first attempt failed in our own code, not the app: the 11th add took about 1s, the test did not wait for the new row, and it counted the add as refused. The test now waits for each new row, and the re-run passed. The test deletes all added rows again afterwards (checked: back to Father + Mother only).</t>
+  </si>
+  <si>
+    <t>Verify the Name field against script injection input</t>
+  </si>
+  <si>
+    <t>Verifying that a script-injection payload entered into a dependent's Name field does not execute, matching the security-check pattern used elsewhere in this project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Enter "&lt;script&gt;alert(1)&lt;/script&gt;" into a dependent's "Name" field
+3. Proceed/save as normal
+4. Verify no JavaScript dialog/alert appears and the payload is treated as plain text</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The Father row's Name was set to "&lt;script&gt;alert(1)&lt;/script&gt;", both Dates of Birth were filled and Father was ticked as Nominee, then Next was clicked. No JavaScript alert or dialog appeared. The field kept the payload as plain text, and no script element containing it was added to the page. There was no validation message on the Name field and no error dialog. The page stayed on Application Form - Phase 2, and Next was blocked only by the usual messages for the sections left blank on purpose (UAN Number, Emergency Contact, etc.). Typed values do not persist, so the next sign-in showed "Amandeep Singh" again.</t>
+  </si>
+  <si>
+    <t>Verify the Name field against SQL injection input</t>
+  </si>
+  <si>
+    <t>A second, distinct payload type on the same field as TC_31 (Name is the only free-text input in Dependent Details, so a second security check exercises a different injection style on the same field rather than skipping coverage) - matching the two-payload-per-field pattern already used elsewhere in this project (e.g. Sign In's TC_11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Enter "' OR '1'='1" into a dependent's "Name" field
+3. Proceed/save as normal
+4. Verify the app behaves normally - no error page, no unexpected data exposure</t>
+  </si>
+  <si>
+    <t>The SQL-injection-style payload should be treated as inert plain text with no unexpected application behaviour</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The Father row's Name was set to "' OR '1'='1", with the same valid rows and Nominee as TC_31, then Next was clicked. The app behaved normally: no error page or error dialog, no JavaScript dialog, and no message on the Name field. The field kept the payload as plain text, the page stayed on Phase 2 Other Details, and only the usual blocking messages appeared for the sections left blank on purpose (e.g. "UAN Number is mandatory", "Contact Number is mandatory"). No unexpected data was shown.</t>
+  </si>
+  <si>
+    <t>Verify whether multiple dependents can share the same Relation value</t>
+  </si>
+  <si>
+    <t>Edge case: checks which Relation values may repeat across dependent rows. Confirmed live 2026-09-25: other relations (e.g. "Brother") may repeat, but the preset Father and Mother relations are unique - a second "Father" or a second "Mother" row is rejected with "Relation exists".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section, fill the Father/Mother rows validly and tick one as Nominee
+2. Click "+ Add Member" twice, setting Relation to "Brother" on both new rows, filling the rest validly
+3. Attempt to proceed - verify neither "Brother" row shows a validation message
+4. Change the second new row's Relation to "Father", attempt to proceed - verify "Relation exists" is shown
+5. Change that row's Relation to "Mother", attempt to proceed - verify "Relation exists" is shown</t>
+  </si>
+  <si>
+    <t>Other relations (e.g. "Brother") may repeat across rows with no validation message. A second "Father" or a second "Mother" row should be rejected with the validation message "Relation exists".</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed (re-run 2026-09-25 after Mother was added to the test). Two members were added, both with Relation "Brother" ("Brother One" 15/08/1995 and "Brother Two" 15/08/1998), with Father/Mother filled validly and Father as Nominee. Next gave no message on either Brother row, nothing anywhere in 1.2 Dependent Details, and no popup, so duplicate "Brother" is allowed. Changing the second Brother to "Father" was rejected with "Relation exists" on both the original Father row and that row. Changing it to "Mother" was rejected with "Relation exists" on both the original Mother row and that row; the Father row then had no message. The test deletes the added rows again afterwards (checked: back to Father + Mother only).</t>
+  </si>
+  <si>
+    <t>Verify how the Name field handles an unusually long input</t>
+  </si>
+  <si>
+    <t>Edge case: checks the length limit on a dependent's Name. Confirmed live 2026-09-25: the Name input has maxlength="200" - up to 200 characters are accepted as-is, and longer input is silently cut to 200 with no validation message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.2 Dependent Details" section
+2. Enter a 160-character string into a dependent's "Name" field, attempt to proceed - verify it is kept in full with no validation message
+3. Enter a 250-character string into the same "Name" field, attempt to proceed
+4. Verify the value is cut to exactly 200 characters and no validation message appears</t>
+  </si>
+  <si>
+    <t>The Name field should accept up to 200 characters as entered. Longer input should be silently cut to 200 characters, with no validation message.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The Name input has maxlength="200". A 160-character name (Father row) was accepted exactly as typed, with no message and no popup on Next. A 250-character name was cut to exactly 200 characters by the input itself, with no message. So long names are accepted up to 200 characters, and anything longer is truncated silently rather than rejected.</t>
+  </si>
+  <si>
+    <t>Verify all static UI text in the "1.3 UAN Details" section</t>
+  </si>
+  <si>
+    <t>Verifying the section heading and all field/question labels in 1.3 UAN Details are present and correctly worded, and that every mandatory field shows the red mandatory asterisk: UAN Number and "member of PF" always, and "withdrawn PF", "member of Pension" and "withdrawn pension" once they are enabled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Verify the sub-heading "1.3 UAN Details"
+3. Verify: "Are you experienced?" (Yes/No), "Are you already a member of PF in your previous establishment?" (Yes/No), "Have you withdrawn the full PF amount from your previous EPF Account?" (Yes/No), "Are you already a member of Pension in your previous establishment?" (Yes/No), "Have you withdrawn the full pension amount from your previous EPS account?" (Yes/No), "UAN Number*", "ESIC number of last company", and the fresher help text "If you are a fresher, watch this video to create your UAN."
+4. Answer "member of PF" = Yes, then "member of Pension" = Yes, so all conditional questions are enabled
+5. Verify which labels show the red mandatory asterisk</t>
+  </si>
+  <si>
+    <t>The section heading and all field/question labels should be present and correctly worded. Every mandatory field should show the red mandatory asterisk: "UAN Number" and "Are you already a member of PF in your previous establishment?" (always mandatory), and "Have you withdrawn the full PF amount from your previous EPF Account?", "Are you already a member of Pension in your previous establishment?" and "Have you withdrawn the full pension amount from your previous EPS account?" (mandatory once enabled). "Are you experienced?" (read-only) and "ESIC number of last company" (optional) should not show one.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. FAILED - confirmed 4/4 (1 live probe + 3 test runs). Text: the header reads "1.3 UAN Details", and all five questions are present and worded as expected, each with Yes/No options. "UAN Number*", "ESIC number of last company" and the help text "If you are a fresher, watch this video to create your UAN." are also present (compared ignoring line breaks, since the help text wraps over 3 lines). All of this passed. Asterisks: "member of PF" was set to Yes (enabling "withdrawn PF" and "member of Pension"), then "member of Pension" set to Yes (enabling "withdrawn pension"); all four questions were then enabled. The only label in the section with the red asterisk is "UAN Number". There is NO asterisk on "Are you already a member of PF in your previous establishment?", "Have you withdrawn the full PF amount from your previous EPF Account?", "Are you already a member of Pension in your previous establishment?" or "Have you withdrawn the full pension amount from your previous EPS account?", not even once enabled. None appeared after Next either, although Next showed "Please select whether you have withdrawn the full PF amount from your previous EPF account." and "Please indicate whether you have withdrawn the full pension amount from your previous EPS account.", so these fields are enforced as mandatory. The screenshot confirms it visually. Correct as expected: no asterisk on "Are you experienced?" or "ESIC number of last company". Choices are not saved, and a fresh sign-in showed them blank again.</t>
+  </si>
+  <si>
+    <t>Verify the "1.3 UAN Details" section toggle expands and collapses correctly</t>
+  </si>
+  <si>
+    <t>Verifying that clicking the +/- toggle on the "1.3 UAN Details" section header correctly collapses and expands that section's fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Click the toggle to collapse the section; verify fields hidden and icon changes to "+"
+3. Click the toggle again to expand; verify fields reappear and icon changes to "-"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The section starts expanded ("-" icon), with the "member of PF" radios and the UAN Number field visible. Clicking the toggle hid them and changed the icon to "+". Clicking it again showed them again and changed the icon back to "-".</t>
+  </si>
+  <si>
+    <t>Verify "Are you experienced?" is read-only and correctly carries over the value from Phase 1</t>
+  </si>
+  <si>
+    <t>Verifying this question is disabled/non-editable on Phase 2 and displays the exact Yes/No value the candidate selected in Phase 1's Experience Details. Confirmed live 2026-09-25: both radio options are disabled, with the correct value pre-checked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note this candidate's "Are you experienced?" answer from Phase 1
+2. Reach the "1.3 UAN Details" section
+3. Verify "Are you experienced?" shows that same value
+4. Attempt to click the other option</t>
+  </si>
+  <si>
+    <t>"Are you experienced?" should be disabled (not editable) and should show the value carried over from Phase 1</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. The account used went through Phase 1 with "Are you experienced?" = Yes. On Phase 2 both the Yes and No options are disabled, with Yes selected. Clicking "No" (both the radio and its label) changed nothing: still Yes selected, No not selected. The fresher account used in TC_38 correspondingly shows No selected.</t>
+  </si>
+  <si>
+    <t>Verify "Are you already a member of PF in your previous establishment?" is enabled regardless of experienced/fresher status</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 on two separate accounts (one experienced=Yes, one experienced=No/fresher): this question is enabled in both cases - unlike ESIC number (below), it is NOT gated by the experienced/fresher status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section on an account whose Phase 1 experienced status is "No" (fresher)
+2. Verify "Are you already a member of PF..." is enabled and answerable
+3. Repeat on an account whose experienced status is "Yes"</t>
+  </si>
+  <si>
+    <t>"Are you already a member of PF in your previous establishment?" should be enabled and answerable regardless of the candidate's experienced/fresher status</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. Checked on two accounts. The fresher account (experienced=No, No selected) was a new pooled account created for this test (iTAP 250575) with Phase 1 Experience Details answered "No"; all five existing pooled accounts are experienced=Yes (read live). The other was the experienced=Yes account. On both, the "member of PF" Yes and No options were enabled, and choosing "No" worked. So this question is not gated by experienced/fresher status. The choice is not saved, and a fresh sign-in showed it blank again.</t>
+  </si>
+  <si>
+    <t>Verify "Are you already a member of PF..." is a mandatory field</t>
+  </si>
+  <si>
+    <t>Verifying that leaving this question unanswered is rejected when attempting to proceed. Exact message confirmed live 2026-09-25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Leave "Are you already a member of PF..." unanswered
+3. Attempt to proceed (click Next or Save)
+4. Verify the validation message appears</t>
+  </si>
+  <si>
+    <t>Should be rejected with the validation message "Please select whether you were a PF member in your previous establishment."</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. With "Are you already a member of PF..." left unanswered (neither option selected), clicking Next showed "Please select whether you were a PF member in your previous establishment." directly under that question, and the page stayed on Other Details.</t>
+  </si>
+  <si>
+    <t>Verify "Have you withdrawn the full PF amount..." stays disabled until "member of PF" is answered "Yes"</t>
+  </si>
+  <si>
+    <t>Verifying this question is disabled while "Are you already a member of PF..." is unanswered, and becomes enabled once it is set to "Yes". Confirmed live 2026-09-25 via direct interaction (not a static read): disabled beforehand, enabled immediately after memberPF=Yes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section, leave "member of PF" unanswered
+2. Verify "Have you withdrawn the full PF amount..." is disabled
+3. Answer "member of PF" = Yes
+4. Verify "Have you withdrawn the full PF amount..." is now enabled</t>
+  </si>
+  <si>
+    <t>"Have you withdrawn the full PF amount..." should be disabled until "member of PF" = Yes, then become enabled</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run. With "member of PF" unanswered, both options of "Have you withdrawn the full PF amount..." were disabled. After choosing "member of PF" = Yes, both became enabled straight away, and Yes on the withdrawn question could be selected. The choices are not saved, and a fresh sign-in showed them blank again with the withdrawn question disabled.</t>
+  </si>
+  <si>
+    <t>Verify "Are you already a member of Pension..." stays disabled until "member of PF" is answered "Yes" - NOT gated by "experienced" or by the PF-withdrawal question</t>
+  </si>
+  <si>
+    <t>IMPORTANT, non-obvious finding confirmed live 2026-09-25: this question's enabling is NOT tied to the candidate's overall experienced status (it stayed disabled for an experienced=Yes account until memberPF was answered), and it unlocks in PARALLEL with the PF-withdrawal question the moment memberPF=Yes - it does NOT additionally wait for the PF-withdrawal question to be answered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section on an experienced=Yes account, leave "member of PF" unanswered
+2. Verify "Are you already a member of Pension..." is disabled
+3. Answer "member of PF" = Yes (leave the PF-withdrawal question unanswered)
+4. Verify "Are you already a member of Pension..." is now enabled, even though the PF-withdrawal question is still unanswered</t>
+  </si>
+  <si>
+    <t>"Are you already a member of Pension..." should become enabled as soon as "member of PF" = Yes, independent of whether the PF-withdrawal question has been answered</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (7.7s). On the experienced=Yes account (read live: Yes selected), with "member of PF" unanswered, both options of "Are you already a member of Pension..." were disabled. After choosing "member of PF" = Yes, with "Have you withdrawn the full PF amount..." still unanswered (neither option selected), both Pension options became enabled straight away. So this question unlocks together with the PF-withdrawal question, and it is not gated by experienced status or by the PF-withdrawal answer. The choices are not saved.</t>
+  </si>
+  <si>
+    <t>Verify "Have you withdrawn the full pension amount..." stays disabled until "member of Pension" is answered "Yes"</t>
+  </si>
+  <si>
+    <t>Verifying this last question in the chain is disabled until "member of Pension" is set to "Yes", confirmed live 2026-09-25 via direct interaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section, progress through "member of PF"=Yes
+2. Verify "Have you withdrawn the full pension amount..." is still disabled while "member of Pension" is unanswered
+3. Answer "member of Pension" = Yes
+4. Verify "Have you withdrawn the full pension amount..." is now enabled</t>
+  </si>
+  <si>
+    <t>"Have you withdrawn the full pension amount..." should be disabled until "member of Pension" = Yes, then become enabled</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (16.2s). After "member of PF" = Yes, with "member of Pension" still unanswered, both options of "Have you withdrawn the full pension amount..." stayed disabled. After choosing "member of Pension" = Yes, both became enabled. The choices are not saved.</t>
+  </si>
+  <si>
+    <t>Verify "Have you withdrawn the full PF amount...", "Are you already a member of Pension...", and "Have you withdrawn the full pension amount..." are each mandatory once enabled</t>
+  </si>
+  <si>
+    <t>CONFIRMED live 2026-09-25: once "member of PF" = Yes enables the three downstream questions, each is independently mandatory - leaving any of them unanswered is rejected with its own distinct validation message when attempting to proceed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Answer "member of PF" = Yes
+3. Leave "withdrawn PF amount", "member of Pension", and "withdrawn pension amount" all unanswered
+4. Attempt to proceed
+5. Verify each has its own validation message</t>
+  </si>
+  <si>
+    <t>Each of the three downstream questions should be rejected with its own message when left unanswered: "Please select whether you have withdrawn the full PF amount from your previous EPF account.", "Please select whether you were a member of the Pension scheme in your previous establishment.", and "Please indicate whether you have withdrawn the full pension amount from your previous EPS account."</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (9.5s). "member of PF" was set to Yes and the three downstream questions left unanswered, then Next was clicked. Each showed its own message directly under that question: "Please select whether you have withdrawn the full PF amount from your previous EPF account." (withdrawn PF), "Please select whether you were a member of the Pension scheme in your previous establishment." (member of Pension), and "Please indicate whether you have withdrawn the full pension amount from your previous EPS account." (withdrawn pension). "member of PF" itself had no message. Observation: the "withdrawn pension" message appears even though that question is still DISABLED at this point, because it only unlocks once "member of Pension" = Yes (see TC_42). The user is told to answer a question they cannot yet answer until they first answer "member of Pension".</t>
+  </si>
+  <si>
+    <t>Verify "ESIC number of last company" is disabled for a fresher (experienced = "No")</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25: for an account whose Phase 1 experienced status is "No", ESIC number is disabled from the outset, unlike UAN Number and "member of PF" which stay enabled regardless of experienced status</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 - the candidate is on Application Form - Phase 2, section "1. Other Details" | This candidate's Phase 1 experienced status was "No"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section on an account whose Phase 1 experienced status is "No"
+2. Attempt to click into / edit "ESIC number of last company"</t>
+  </si>
+  <si>
+    <t>"ESIC number of last company" should be disabled and not accept input for a fresher (experienced = "No")</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (7.5s). On the fresher account (iTAP 250575, "Are you experienced?" read live as No), "ESIC number of last company" was disabled. Clicking into it and typing "3112345678" was not accepted, and the field stayed blank.</t>
+  </si>
+  <si>
+    <t>Verify "ESIC number of last company" is enabled when experienced = "Yes"</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25: for an account whose Phase 1 experienced status is "Yes", ESIC number is enabled from the outset</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 - the candidate is on Application Form - Phase 2, section "1. Other Details" | This candidate's Phase 1 experienced status was "Yes"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section on an account whose Phase 1 experienced status is "Yes"
+2. Verify "ESIC number of last company" is enabled and accepts input</t>
+  </si>
+  <si>
+    <t>"ESIC number of last company" should be enabled and accept input when experienced = "Yes"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (7.7s). On the experienced=Yes account (read live: Yes selected), with no PF/Pension question answered, "ESIC number of last company" was enabled from the start. It accepted "3112345678", which was still there after leaving the field. Typed values are not saved, and a fresh sign-in showed the field blank again.</t>
+  </si>
+  <si>
+    <t>Verify UAN Number is enabled and mandatory regardless of experienced/fresher status</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 on a fresher (experienced=No) account: UAN Number stays enabled (unlike ESIC), and its blank-field validation message was confirmed in the same run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section on a fresher (experienced=No) account
+2. Verify "UAN Number" is enabled and blank
+3. Leave it blank and attempt to proceed
+4. Verify the validation message "UAN Number is mandatory" appears under the UAN Number field
+5. Repeat steps 1-4 on an experienced=Yes account</t>
+  </si>
+  <si>
+    <t>On both a fresher (experienced=No) and an experienced=Yes account, UAN Number should be enabled, and rejected with the message "UAN Number is mandatory" when left blank.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed (26.8s; extended 2026-09-25 to cover both accounts). Fresher account (iTAP 250575, "Are you experienced?" read live as No): UAN Number was enabled (unlike ESIC, see TC_44) and blank, and Next with it left blank showed "UAN Number is mandatory" directly under the field. Experienced=Yes account ("Are you experienced?" read live as Yes): the same result - enabled, blank, and "UAN Number is mandatory" under the field on Next. So UAN Number is enabled and mandatory regardless of experienced/fresher status. Note: the first attempt of the extended test never reached the app (the sign-in page loaded blank, and our own sign-in step timed out); that is an environment issue, not a result. The re-run passed. The value is not saved; both accounts still show UAN Number blank on a fresh sign-in.</t>
+  </si>
+  <si>
+    <t>Verify UAN Number rejects a malformed value</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25: a 5-digit UAN Number is rejected with a specific format-validation message, distinct from the mandatory-field message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Enter a 5-digit value (e.g. "12345") into "UAN Number"
+3. Attempt to proceed
+4. Verify the validation message appears</t>
+  </si>
+  <si>
+    <t>A malformed UAN Number should be rejected with the message "UAN Number is invalid"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (10.0s). "12345" (5 digits) was entered into UAN Number and kept as typed. Clicking Next showed "UAN Number is invalid" directly under the UAN Number field, and not the "UAN Number is mandatory" message.</t>
+  </si>
+  <si>
+    <t>Verify UAN Number accepts a valid 12-digit value</t>
+  </si>
+  <si>
+    <t>UAN (Universal Account Number, issued by EPFO) is a standard 12-digit numeric identifier. The sample value shown in the user's own screenshot ("876578765432") is 12 digits, consistent with this. The exact valid length has been confirmed INVALID at 5 digits, but not yet independently confirmed as ACCEPTED at exactly 12 - that positive case still needs a live check before this can be marked Passed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Enter a valid 12-digit value into "UAN Number" (e.g. "876578765432")
+3. Attempt to proceed
+4. Verify no validation message appears for UAN Number</t>
+  </si>
+  <si>
+    <t>A 12-digit numeric UAN Number should be accepted without a validation error</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (8.8s). "876578765432" (12 digits, the sample value from the user's screenshot) was entered into UAN Number and kept as typed. Clicking Next gave no message on the UAN Number field and no UAN-related message anywhere on the page, so a 12-digit value is accepted. Next was still blocked, on purpose, by the other sections left blank (Blood group, Religion, Dependent Date of Birth, member of PF, Emergency Contact), so this pooled account never advances. The typed value is not saved.</t>
+  </si>
+  <si>
+    <t>Verify the fresher help text/video link's actual visibility condition</t>
+  </si>
+  <si>
+    <t>FLAGGED, not asserted either way: the static text "If you are a fresher, watch this video to create your UAN." is visible in the user's own screenshot, but a live check on a fresher (experienced=No) account found the link NOT visible via one specific locator strategy. That result is not trusted as a genuine finding - it may be a locator/matching issue on the automation side rather than a real app behaviour - so this needs a clean re-check (e.g. searching the raw page HTML rather than a single Playwright text-locator) before asserting when this link does or doesn't show.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section on a fresher (experienced=No) account and check for the video link/help text
+2. Repeat on an experienced=Yes account
+3. Determine the actual visibility rule (always shown / only for freshers / tied to some other condition) using a reliable check, not a single locator attempt</t>
+  </si>
+  <si>
+    <t>To be confirmed live with a more reliable check - do not assume the link is conditionally hidden based on one inconclusive automated attempt</t>
+  </si>
+  <si>
+    <t>Not yet automated. (Blocked: YouTube is blocked on this network, so the video's content/playability can't be verified from here.)</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Verify the UAN Number field against injection input</t>
+  </si>
+  <si>
+    <t>Verifying that a script/SQL-injection-style payload entered into UAN Number does not execute and is rejected as an invalid format (UAN Number is strictly numeric), matching the security-check pattern used elsewhere in this project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Enter "&lt;script&gt;alert(1)&lt;/script&gt;" into "UAN Number"
+3. Attempt to proceed
+4. Verify no JavaScript dialog/alert appears, and the payload is rejected (matching the same "UAN Number is invalid" format-rejection already confirmed for non-numeric input) rather than causing any unexpected behaviour</t>
+  </si>
+  <si>
+    <t>The script payload should be treated as inert text and rejected by the existing numeric-format validation, with no JavaScript alert/dialog ever appearing</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (9.9s). "&lt;script&gt;alert(1)&lt;/script&gt;" was entered into UAN Number. The field cuts input to 12 characters, so it kept "&lt;script&gt;aler" as plain text. Clicking Next showed no JavaScript alert or dialog, no script element containing the payload was added to the page, and the page stayed on Application Form - Phase 2. The value was rejected with "UAN Number is invalid" directly under the field, the same format message as TC_47. The only popup was the usual "Information" one ("Please complete all mandatory fields (including Nominee, if not already selected) to proceed"), because no Nominee was ticked in this test; it is not an error. The typed value is not saved.</t>
+  </si>
+  <si>
+    <t>Verify all static UI text in the "1.4 Emergency Contact" section</t>
+  </si>
+  <si>
+    <t>Verifying the section heading and all field labels in 1.4 Emergency Contact are present and correctly worded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Verify the sub-heading "1.4 Emergency Contact"
+3. Verify field labels: "Name of person to be contacted*", "Relation*", "Contact Number 1*", "Contact Number 2"</t>
+  </si>
+  <si>
+    <t>The section heading and all field labels should be present and correctly worded, with mandatory fields (Name, Relation, Contact Number 1) showing the red asterisk and Contact Number 2 not showing one</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (8.6s). The header reads "1.4 Emergency Contact". The column labels read "Name of person to be contacted", "Relation", "Contact Number 1" and "Contact Number 2". The first three each carry the red mandatory asterisk; "Contact Number 2" has none. The section has exactly 2 contact rows and no add button.</t>
+  </si>
+  <si>
+    <t>Verify the "1.4 Emergency Contact" section toggle expands and collapses correctly</t>
+  </si>
+  <si>
+    <t>Verifying that clicking the +/- toggle on the "1.4 Emergency Contact" section header correctly collapses and expands that section's fields - the fourth and final subsection toggle in "1. Other Details" (matching TC_12 for 1.1, TC_14 for 1.2, TC_36 for 1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Click the toggle to collapse the section; verify fields hidden and icon changes to "+"
+3. Click the toggle again to expand; verify fields reappear and icon changes to "-"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (8.9s). The section starts expanded ("-" icon), with the contact Name and Contact Number 1 fields visible. Clicking the toggle hid them and changed the icon to "+". Clicking it again showed them again and changed the icon back to "-".</t>
+  </si>
+  <si>
+    <t>Verify "Name of person to be contacted" is a mandatory field</t>
+  </si>
+  <si>
+    <t>Verifying that leaving an Emergency Contact row's Name blank is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Leave the first row's "Name of person to be contacted" blank, fill Relation and Contact Number 1 validly
+3. Attempt to proceed (click Next or Save)
+4. Verify a validation message appears for Name</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (11.3s). First contact row: Name left blank, Relation "Brother", Contact Number 1 "9876543210". Clicking Next showed "Name is mandatory" directly under that row's Name field, and no message on its Relation or Contact Number 1. The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verify Relation is a mandatory field</t>
+  </si>
+  <si>
+    <t>Verifying that leaving an Emergency Contact row's Relation unselected is rejected when attempting to proceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Leave the second row's "Relation" unselected, fill Name and Contact Number 1 validly
+3. Attempt to proceed
+4. Verify a validation message appears for Relation</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (11.5s). Following the Excel steps on the SECOND contact row: Name "Sunita Devi" and Contact Number 1 "9876543211" filled, Relation left unselected. The first row was filled validly ("Ravi Kumar" / Brother / 9876543210). Clicking Next showed "Relation is mandatory" directly under the second row's Relation, and no message on its Name or Contact Number 1. The first row had no message at all. So a partly filled second contact is validated even though the second contact as a whole may be left blank. The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verifying the Relation dropdown lists exactly the expected options, correctly worded. Confirmed live 2026-09-25 and independently confirmed by the user's own screenshot the same day - both match exactly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Click a row's "Relation" dropdown
+3. Verify the list of options shown</t>
+  </si>
+  <si>
+    <t>The Relation dropdown should show exactly these options, in this order: "Husband", "Wife", "Father", "Mother", "Brother", "Sister", "Father-In-Law", "Mother-In-Law", "Son", "Daughter", "Friend", "Other"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (7.2s). The Relation dropdown on BOTH contact rows lists exactly, in order: "Husband", "Wife", "Father", "Mother", "Brother", "Sister", "Father-In-Law", "Mother-In-Law", "Son", "Daughter", "Friend", "Other" (blank placeholder excluded). This matches the earlier live check and the user's screenshot.</t>
+  </si>
+  <si>
+    <t>Verify Contact Number 1 is a mandatory field</t>
+  </si>
+  <si>
+    <t>Verifying that leaving an Emergency Contact row's Contact Number 1 blank is rejected when attempting to proceed. CONFIRMED by the user (2026-09-25) as a simple, independent rule: Contact Number 1 is mandatory regardless of Contact Number 2; it is not a cross-field "either one" requirement - an earlier revision of this row briefly (incorrectly) framed it that way before the user corrected it back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Leave "Contact Number 1" blank, fill Name and Relation validly
+3. Attempt to proceed
+4. Verify a validation message appears for Contact Number 1</t>
+  </si>
+  <si>
+    <t>Contact Number 1 should be rejected with a mandatory-field validation message when left blank</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (9.9s). First contact row: Name "Ravi Kumar", Relation "Brother", Contact Number 1 left blank (and Contact Number 2 blank). Clicking Next showed "Contact Number is mandatory" directly under that row's Contact Number 1, and no message on its Name, Relation or Contact Number 2. The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verify Contact Number 1 rejects a malformed value</t>
+  </si>
+  <si>
+    <t>Verifying that an invalid Contact Number 1 (wrong digit count) is rejected. Exact message confirmed live 2026-09-25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Enter a 5-digit value into "Contact Number 1"
+3. Attempt to proceed
+4. Verify the validation message appears</t>
+  </si>
+  <si>
+    <t>A malformed Contact Number 1 should be rejected with the message "Contact Number is not valid"</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (9.8s). First contact row: Name "Ravi Kumar", Relation "Brother", Contact Number 1 "12345" (5 digits). Clicking Next showed "Contact Number is not valid" directly under that row's Contact Number 1, and no message on the other fields of the row. Note: the Contact Number inputs have maxlength="10" (read from the DOM). The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verify Contact Number 2 is optional</t>
+  </si>
+  <si>
+    <t>Verifying that leaving Contact Number 2 blank does not block proceeding, since it carries no mandatory asterisk. CONFIRMED by the user (2026-09-25) as a simple, independent rule, not tied to Contact Number 1's own state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Fill Name, Relation, and Contact Number 1 validly for both rows, leaving "Contact Number 2" blank on both
+3. Attempt to proceed</t>
+  </si>
+  <si>
+    <t>Leaving "Contact Number 2" blank should NOT block proceeding</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (10.4s). Both contact rows were filled validly ("Ravi Kumar" / Brother / 9876543210 and "Sunita Devi" / Sister / 9876543211), with Contact Number 2 left blank on both. Clicking Next raised no validation message anywhere in 1.4 Emergency Contact and no Contact Number message on the page, so a blank Contact Number 2 does not block this section. The remaining messages came only from the other sections, which were left blank on purpose so this pooled account never advances: Blood group, Religion, Dependent Date of Birth, member of PF, and UAN Number. The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verify Contact Number 2, if filled, is format-validated the same way as Contact Number 1</t>
+  </si>
+  <si>
+    <t>Verifying that Contact Number 2, although optional, is format-validated the same way as Contact Number 1 when it is filled in - a malformed value is rejected with the same "Contact Number is not valid" message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Enter a malformed value (e.g. 5 digits, "12345") into "Contact Number 2"
+3. Attempt to proceed
+4. Verify the validation message "Contact Number is not valid" appears under Contact Number 2</t>
+  </si>
+  <si>
+    <t>A malformed Contact Number 2 should be rejected with the validation message "Contact Number is not valid" - the same format rule and wording as Contact Number 1</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (10.9s). Confirmed live: Contact Number 2 IS format-validated like Contact Number 1. First contact row: Name "Ravi Kumar", Relation "Brother", Contact Number 1 "9876543210" (valid), Contact Number 2 "12345" (5 digits). Clicking Next showed "Contact Number is not valid" directly under Contact Number 2, the same wording as Contact Number 1's rule (TC_57), and no message on Contact Number 1. The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verify Emergency Contact Relation does not restrict marriage-dependent options when the candidate's Marital Status is "Single"</t>
+  </si>
+  <si>
+    <t>Confirmed defect, found and reported directly by the user (2026-09-25): for a candidate whose Marital Status (carried over from Phase 1, shown read-only in 1.1 Other Details) is "Single", the Emergency Contact Relation dropdown still accepts marriage-dependent relations such as "Husband", "Wife", "Father-In-Law", and "Mother-In-Law" without any restriction or warning - which is logically inconsistent for someone who has never married.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed and submitted Phase 1 - the candidate is on Application Form - Phase 2, section "1. Other Details" | This candidate's Marital Status (from Phase 1) is "Single"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "1.4 Emergency Contact" on a candidate whose Marital Status is "Single"
+2. Select "Husband" (or "Wife"/"Father-In-Law"/"Mother-In-Law") as the Relation for an emergency contact
+3. Fill the rest of the row validly and attempt to proceed</t>
+  </si>
+  <si>
+    <t>Selecting a marriage-dependent Relation (Husband/Wife/Father-In-Law/Mother-In-Law) should be rejected or restricted for a candidate whose Marital Status is "Single", since such a relation cannot logically exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported directly by the user (2026-09-25): confirmed on the live app that these marriage-dependent Relation options are accepted without any restriction for a Single candidate, with no validation message and no submission block.
+Automated 2026-09-25: FAILED, confirmed 3/3 runs (16.9s / 16.3s / 16.4s). Account: Marital Status read live as "Single". The first contact row's Relation dropdown offers "Husband", "Wife", "Father-In-Law" and "Mother-In-Law". Each was selected in turn (with Name "Ravi Kumar" and Contact Number 1 "9876543210") and Next was clicked. None of the four raised any validation message on the Relation field, and there was no warning or restriction, confirming the user's report. Next was blocked only by the other sections left blank on purpose.</t>
+  </si>
+  <si>
+    <t>Verify the Name of person to be contacted field against script injection input</t>
+  </si>
+  <si>
+    <t>Verifying that a script-injection payload entered into an Emergency Contact's Name field does not execute, matching the security-check pattern used elsewhere in this project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.4 Emergency Contact" section
+2. Enter "&lt;script&gt;alert(1)&lt;/script&gt;" into a row's "Name of person to be contacted"
+3. Proceed/save as normal
+4. Verify no JavaScript dialog/alert appears and the payload is treated as plain text</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (10.8s). The first contact's "Name of person to be contacted" was set to "&lt;script&gt;alert(1)&lt;/script&gt;", with Relation "Brother" and Contact Number 1 "9876543210", then Next was clicked. No JavaScript alert or dialog appeared. The field kept the payload as plain text, no script element containing it was added to the page, and there was no validation message on any field of that row. The page stayed on Application Form - Phase 2, and Next was blocked only by the usual messages for the other sections left blank on purpose. The typed values are not saved.</t>
+  </si>
+  <si>
+    <t>Verify clicking Next, once all of 1.1-1.4 are validly completed, renders the "2. Upload Documents" section</t>
+  </si>
+  <si>
+    <t>Verifying the final transition out of "1. Other Details" (all four subsections - Other Details, Dependent Details, UAN Details, Emergency Contact - combined on one continuous page with one shared Save/Next pair at the bottom) into Phase 2's second and final step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill every mandatory field across 1.1, 1.2, 1.3, and 1.4 with valid data
+2. Click "Next"
+3. Verify the step indicator shows "2. Upload Documents" as the current step
+4. Verify the Upload Documents section renders</t>
+  </si>
+  <si>
+    <t>Once all mandatory fields across 1.1-1.4 are validly filled, clicking "Next" should render the "2. Upload Documents" section, with the step indicator showing step 1 as completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated 2026-09-25. Passed (29.0s). The first attempt failed on our own locator: the step indicator renders the "2." disc and the "Upload Documents" label as separate elements. The locator was fixed and the re-run passed. Run on the SPARE pooled account "Divorced" (995131365728; Marital Status read live as Divorced, so Date Of Marriage is disabled), never on the main single/fresher accounts. Every mandatory field was filled validly: Blood group A+, Religion Hinduism, Father/Mother Date of Birth 15/08/1965 / 15/08/1970 with Father as Nominee, member of PF = No, UAN Number 876578765432, and both Emergency Contact rows ("Ravi Kumar" / Brother / 9876543210 and "Sunita Devi" / Sister / 9876543211). Clicking Next raised no validation message and no dialog. The page left Other Details and rendered "2. Upload Documents": the note "Max 2 files per document...", "Click to Upload General Documents" with Aadhaar Card / PAN Card / Latest Photo / Bank proof / UAN Profile, then Qualification, Experience and Dependent (Father/Mother) document sections, the consent checkbox and a Submit button. The step indicator changed: step 2 "Upload Documents" is now the dark current disc (it was pale before), and step 1 no longer shows its "1." number, consistent with a completed marker.
+Flagged: the second Emergency Contact row had to be filled. With it left blank, Next was rejected with "Name is mandatory", "Relation is mandatory" and "Contact Number is mandatory" on that row (checked live on this account). This contradicts the ruling that the second contact may be left blank.
+Reversibility (checked live): the successful Next SAVED all the entered values. A fresh sign-in still lands on 1. Other Details (normal fast path), showing the saved values. Clicking the "Other Details" step label or circle does nothing, and there is no Back button on Upload Documents. Nothing on Upload Documents was touched: no file uploaded, no Submit.</t>
+  </si>
+  <si>
+    <t>Verify the Sign Out button actually signs the candidate out of Phase 2</t>
+  </si>
+  <si>
+    <t>TC_01 only verifies the Sign out button is VISIBLE on the Phase 2 header - it does not verify clicking it actually works. This dedicated functional test closes that gap, matching the equivalent already covered in Phase 1 (Phase1 sheet TC_38).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach any section of Phase 2
+2. Click the "Sign out" button
+3. Verify the candidate is redirected away from the application (e.g. to the Sign In page)
+4. Attempt to navigate back to the Phase 2 URL directly
+5. Verify authenticated content is no longer accessible without signing in again</t>
+  </si>
+  <si>
+    <t>Clicking "Sign out" should end the candidate's session and redirect away from Phase 2; the form should not be directly accessible again without re-authenticating</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed (14.0s). The first attempt failed in our own test: Sign out opens a confirmation dialog, "Confirmation - Are you sure you want to log out?" (Yes / No), which the test did not answer. The step was added and the re-run passed. From Phase 2 "1. Other Details", clicking "Sign out" and confirming "Yes" redirected to the Candidate Login page (/p/candidatelogin, title "Mendix - Candidate Login", Aadhar Number field shown). Afterwards no authenticated Phase 2 content could be reached: browser Back stayed on Candidate Login (#/candidatelogin), a page reload stayed on Candidate Login, and re-opening the URL Phase 2 had been on also redirected to /p/candidatelogin. That URL is just the app root "/", as Phase 2 has no URL of its own. In all four checks there was no Phase 2 title and no Other Details field.</t>
+  </si>
+  <si>
+    <t>Verify selecting 'No' for Pension membership clears the withdrawn-pension requirement</t>
+  </si>
+  <si>
+    <t>Verifying that once "member of PF" = Yes has made the three downstream questions mandatory, answering "Are you already a member of Pension..." = No removes the requirement on "Have you withdrawn the full pension amount..." - that question stays disabled, its validation message disappears, and it no longer blocks proceeding. Guards against candidates without pension history being blocked by a question they cannot answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "1.3 UAN Details" section
+2. Answer "member of PF" = Yes and attempt to proceed, so the "withdrawn pension" message ("Please indicate whether you have withdrawn the full pension amount from your previous EPS account.") is shown
+3. Answer "Are you already a member of Pension..." = No
+4. Verify "Have you withdrawn the full pension amount..." stays disabled and its message has disappeared
+5. Answer "Have you withdrawn the full PF amount..." = Yes and attempt to proceed again
+6. Verify no pension-related validation message appears</t>
+  </si>
+  <si>
+    <t>After "member of PF" = Yes and "member of Pension" = No, "Have you withdrawn the full pension amount..." should stay disabled, its validation message should disappear, and it should not block Next - with "withdrawn PF" also answered, no pension-related message should appear on Next.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25. Passed on first run (12.6s). Experienced=Yes account. After "member of PF" = Yes and a first Next, the "withdrawn pension" message ("Please indicate whether you have withdrawn the full pension amount from your previous EPS account.") was on screen under that question. After choosing "member of Pension" = No, both "withdrawn pension" options stayed disabled and its message was gone. With "withdrawn PF" = Yes as well, a second Next gave no pension-related message anywhere, and nothing under "member of Pension", "withdrawn pension" or "withdrawn PF"; "withdrawn pension" was still disabled. So Pension = No correctly removes the withdrawn-pension requirement and it does not block candidates without pension history. Next was still blocked only by the other sections left blank on purpose (Blood group, Religion, Dependent Date of Birth, UAN Number, Emergency Contact). The choices are not saved.</t>
+  </si>
+  <si>
+    <t>Verify the static note text and Document Upload Instructions link on "2. Upload Documents"</t>
+  </si>
+  <si>
+    <t>Verifying the file-limit note bar and the instructions link are present and correctly worded on the Upload Documents page.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Verify the note text: "Note: Max 2 files per document (except Experience documents: max 10) | Max 5 MB per file | File name : 256 characters max | PDF, PNG, JPEG, JPG only"
+3. Verify the "Click Here To See Document Upload Instructions" link is present</t>
+  </si>
+  <si>
+    <t>The note text and the instructions link should both be present and exactly as worded above.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed: the note text reads exactly "Note: Max 2 files per document (except Experience documents: max 10) | Max 5 MB per file | File name : 256 characters max | PDF, PNG, JPEG, JPG only", and the instructions link ("Click Here To See Document Upload Instructions") is present. Corrected from an earlier Excel transcription typo (missing "Note: " prefix, missing space before the colon in "File name :"), not an app defect.</t>
+  </si>
+  <si>
+    <t>Verify the step indicator shows "Other Details" completed and "Upload Documents" as the current step</t>
+  </si>
+  <si>
+    <t>Verifying the step circles/labels correctly reflect progress, mirroring Phase 1's step-indicator behavior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Verify the "Other Details" step circle shows a checkmark (completed)
+3. Verify the "Upload Documents" step circle shows "2." and is the current/highlighted step, connected by a line to "Other Details"</t>
+  </si>
+  <si>
+    <t>The "Other Details" step should show a checkmark as completed; "Upload Documents" should be the current step, labelled "2."</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `divorced` account: after a real successful Next on Other Details, the "Other Details" step circle shows the green completed checkmark image (the "1." numeral span is still in the DOM but hidden via its own hide-desktop/hide-phone classes), and the "Upload Documents" step circle shows "2." with the current-step background color rgb(50, 43, 124). Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify all static UI text and mandatory asterisks in "Click to Upload General Documents"</t>
+  </si>
+  <si>
+    <t>Verifying the section heading and all 5 document field labels are present, correctly worded, and carry the mandatory asterisk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Verify the sub-heading "Click to Upload General Documents"
+3. Verify field labels, each with a red mandatory asterisk: "Aadhaar Card (Both the front and back of card)*", "PAN Card*", "Latest Photo (Passport size)*", "Upload any one: Cancelled Cheque (with Name) / Passbook Copy / Last 3 Months Bank Statement*", "UAN Profile*"
+4. Verify each has a "Choose File" control</t>
+  </si>
+  <si>
+    <t>The heading and all 5 field labels should be present, correctly worded, and each should show the red mandatory asterisk.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `divorced` account: heading "Click to Upload General Documents" present, and all 5 field labels present, worded exactly as expected, each with the red mandatory asterisk: "Aadhaar Card (Both the front and back of card)*", "PAN Card*", "Latest Photo (Passport size)*", "Upload any one: Cancelled Cheque (with Name) / Passbook Copy / Last 3 Months Bank Statement*", "UAN Profile*". Each has a "Choose File" control (5 total). Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify all static UI text and mandatory asterisks in "Click to Upload Qualification Documents"</t>
+  </si>
+  <si>
+    <t>Verifying the section heading and 3 document field labels, and that only "Highest Qualification" is mandatory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Verify the sub-heading "Click to Upload Qualification Documents"
+3. Verify field labels: "10th" and "12th" (neither with an asterisk), "Highest Qualification (Upload any one of Degree/Provisional Degree Certificate/Final Year Marksheet)*" (with an asterisk)</t>
+  </si>
+  <si>
+    <t>The heading and all 3 field labels should be present and correctly worded; only "Highest Qualification" should show the red mandatory asterisk.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `divorced` account: heading "Click to Upload Qualification Documents" present. "10th" and "12th" labels present with NO asterisk on either. "Highest Qualification (Upload any one of Degree/Provisional Degree Certificate/Final Year Marksheet)" present WITH the red mandatory asterisk. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify "Click to Upload Experience Documents" is present and correctly worded for an experienced candidate</t>
+  </si>
+  <si>
+    <t>Verifying this section renders with its one mandatory field for an experienced=Yes account.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1., on an experienced=Yes account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" on an experienced=Yes account
+2. Verify the sub-heading "Click to Upload Experience Documents"
+3. Verify the field label: "Upload any one: Three months salary slip / Last CTC letter / Promotion or Increment letter*"</t>
+  </si>
+  <si>
+    <t>The section should be present, with the one field labelled and mandatory as above.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `divorced` account (experienced=Yes per utils/Phase2TestCandidates.js): heading "Click to Upload Experience Documents" present, with the single field labelled "Upload any one: Three months salary slip / Last CTC letter / Promotion or Increment letter" and marked mandatory (red asterisk). Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify "Click to Upload Experience Documents" does not appear for a fresher (experienced=No) candidate</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 via a throwaway signup: only "Click to Upload General Documents", "Click to Upload Qualification Documents" and "Click to Upload Dependent Documents" rendered on Upload Documents - no Experience Documents block at all.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1., on an experienced=No (fresher) account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" on a fresher (experienced=No) account
+2. Verify the "Click to Upload Experience Documents" heading is NOT present anywhere on the page</t>
+  </si>
+  <si>
+    <t>The Experience Documents section should not render at all for a fresher.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `fresherUploads` account (experienced=No): the "Click to Upload Experience Documents" heading and section are entirely absent from the page - zero matches for that groupbox and zero matches for that heading text anywhere on the page. General Documents, Qualification Documents and Dependent Documents sections are all still present (proves this is a targeted absence, not a broken/empty page). Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a document-upload block appears for every non-deceased dependent</t>
+  </si>
+  <si>
+    <t>Verifying "Click to Upload Dependent Documents" renders one block per dependent who is not marked deceased, headed "{Name} - {Relation}'s Documents", each with Aadhaar Card* and Photo*. Confirmed by the user (2026-09-25): all dependents get a document block except any marked deceased.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" on an account whose 1.2 Dependent Details has Father and Mother, neither marked deceased
+2. Verify the sub-heading "Click to Upload Dependent Documents"
+3. Verify one block per dependent, headed "{Name} - {Relation}'s Documents" (e.g. "Amandeep Singh - Father's Documents")
+4. Verify each block has "Aadhaar Card*" and "Photo*", both mandatory</t>
+  </si>
+  <si>
+    <t>One document block per non-deceased dependent should appear, each correctly headed and with both fields mandatory.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `divorced` account: read Father (Amandeep Singh) and Mother (Kashish Kaur) rows on 1. Other Details first - neither has a Date of Demise set, so both are expected. After Next, "Click to Upload Dependent Documents" showed exactly 2 blocks, headed "Amandeep Singh - Fathers Documents" and "Kashish Kaur - Mothers Documents" (apostrophe rendered as part of the heading text, matching the {Name} - {Relation}'s Documents pattern), each with "Aadhaar Card*" and "Photo*". Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a dependent marked deceased (Date of Demise set) does NOT get a document-upload block</t>
+  </si>
+  <si>
+    <t>Confirmed by the user (2026-09-25) from their own use of the app: with Father marked as deceased and no other members added, only Mother's document block appeared.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1., on an account whose 1.2 Dependent Details has one dependent (e.g. Father) marked deceased via a Date of Demise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" on an account with one dependent marked deceased
+2. Verify "Click to Upload Dependent Documents" shows a block ONLY for the non-deceased dependent(s)
+3. Verify no block is shown for the deceased dependent</t>
+  </si>
+  <si>
+    <t>No document block should appear for a dependent marked deceased; only non-deceased dependents should have one.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Built one new dedicated account via a genuine fresh signup (Aadhaar 457263275671, iTAP 250578, experienced=Yes) specifically for this test, since neither `divorced` nor `fresherUploads` has a deceased dependent and marking one on either would have permanently altered their existing saved state. On Other Details: Father (Amandeep Singh, DOB 15/08/1965) given a Date of Demise of 15/08/2020 (after DOB, before today); Mother (Kashish Kaur, DOB 15/08/1970) left non-deceased and made the Nominee instead (confirmed rule: a Nominee cannot have a Date of Demise). UAN Details and both Emergency Contact rows filled validly. Next succeeded with zero validation messages. On Upload Documents, "Click to Upload Dependent Documents" showed exactly ONE block, headed "Kashish Kaur - Mothers Documents" - no block appeared for the deceased Father. Matches Expected exactly. Account added to utils/Phase2TestCandidates.js as `deceasedDependent`, reserved for this test only.</t>
+  </si>
+  <si>
+    <t>Verify the consent checkbox text is present, correctly worded, and unchecked by default</t>
+  </si>
+  <si>
+    <t>Verifying the consent statement candidates must accept before submitting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Verify the checkbox text: "I confirm that the details provided by me are accurate to the best of my knowledge. I consent to the collection, processing, and storage of my personal data by Mankind for recruitment purposes."
+3. Verify the checkbox is unchecked by default</t>
+  </si>
+  <si>
+    <t>The consent text should be present and exactly as worded above, unchecked by default.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on the `divorced` account: consent text present, worded exactly "I confirm that the details provided by me are accurate to the best of my knowledge. I consent to the collection, processing, and storage of my personal data by Mankind for recruitment purposes.", and the checkbox is unchecked by default. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify "Click Here To See Document Upload Instructions" downloads a complete, correct instructions document</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - the link triggers a download of a Mendix-hosted "Document Upload Instruction.pdf" file (not a modal). Extended 2026-09-28: that only proved the download MECHANISM works, not that the document's CONTENT is correct. The user provided screenshots (2026-09-28) of "1. For General Documents", "2. For Qualification Documents Upload" and "4. For Dependent Documents &amp; Final Submission" - whether a "3. For Experience Documents Upload" section exists in between is not yet confirmed and should be discovered live, not assumed either way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Click "Click Here To See Document Upload Instructions" and retrieve the downloaded PDF
+3. Verify it loads/downloads as "Document Upload Instruction.pdf"
+4. Extract its text and verify the note text ("Note: Max 2 files per document (except Experience documents : max 10) | Max 5 MB per file | ...") appears
+5. Verify all 4 section headings appear, in order: "1. For General Documents", "2. For Qualification Documents Upload", "3. For Experience Documents Upload", "4. For Dependent Documents &amp; Final Submission"
+6. Verify each of the 4 sections has at least one embedded image/screenshot alongside it</t>
+  </si>
+  <si>
+    <t>The link should download "Document Upload Instruction.pdf", and that PDF should contain the note text and all 4 section headings in order, each with an accompanying screenshot - confirming the reference document is complete, not just that the download itself succeeds.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Download mechanism confirmed earlier (link opens a new tab pointing directly at a Mendix /file?guid=... URL - Chromium renders it inline rather than firing a save-as download; fetched it directly via an authenticated request to that URL, 609490 bytes, parsed with pdf-parse). Confirmed: all 4 section headings are present - "1. For General Documents", "2. For Qualification Documents Upload", "3. For Experience Documents Upload", "4. For Dependent Documents &amp; Final Submission" (2 pages total, headings not in strict top-to-bottom reading order in the extracted text, but all 4 genuinely exist - "3. For Experience Documents Upload" is NOT missing). 8 embedded images total (6 on page 1, 2 on page 2) - real screenshots accompany the sections. MISMATCH FOUND: the PDF's own note text reads "Note: Max 2 files per document (except Experience documents : max 10) | Max 5 MB per file | PDF, PNG, JPEG, JPG only" - it is MISSING the "File name : 256 characters max |" clause that the live Upload Documents page shows. Flagged for a ruling: the reference document is out of sync with the live page on this one point.</t>
+  </si>
+  <si>
+    <t>Verify unsupported file types cannot be selected for a document slot</t>
+  </si>
+  <si>
+    <t>Verifying that the file input's accept attribute (image/jpeg,image/jpg,image/png,application/pdf) prevents a real user from ever selecting an unsupported file type through the browser's native file picker, matching the note "PDF, PNG, JPEG, JPG only". Corrected 2026-09-26: an earlier attempt tested this via Playwright's setInputFiles(), which bypasses the native OS picker entirely and forces a file onto the input directly - something no real user can do through the UI. The user tried this manually and confirmed an unsupported file cannot even be dropped/selected, so there is no genuine rejection moment to show a message for. Not a defect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Click "Choose File" on any document slot
+3. In the OS file picker, verify only PDF, PNG, JPEG and JPG files are selectable (confirmed live: the input's accept attribute is "image/jpeg,image/jpg,image/png,application/pdf")
+4. Attempt to drag-and-drop an unsupported file type (e.g. .gif) onto the dropzone - verify it is not accepted</t>
+  </si>
+  <si>
+    <t>Unsupported file types should not be selectable via the OS file picker, and should not be accepted via drag-and-drop either. No in-app rejection message is needed since selection itself is prevented.</t>
+  </si>
+  <si>
+    <t>Confirmed 2026-09-26: the file input's accept attribute correctly restricts selection to image/jpeg, image/jpg, image/png and application/pdf. The user manually confirmed an unsupported file cannot be selected or dropped at all. Not a defect - retracted from the earlier (incorrect) automation-bypass framing.</t>
+  </si>
+  <si>
+    <t>Verify a valid PDF file is accepted for a General Document slot</t>
+  </si>
+  <si>
+    <t>Verifying PDF, one of the 4 stated allowed formats, is genuinely accepted (not just listed in the note).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a valid .pdf file into a General Document slot (e.g. PAN Card)
+3. Verify it is accepted into that slot's file list with no error</t>
+  </si>
+  <si>
+    <t>The PDF file should be accepted with no error.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: uploaded test.pdf into the empty Aadhaar Card (General Documents) slot - accepted into the file list (test.pdf shown), no alert/error rendered. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a valid PNG file is accepted for a General Document slot</t>
+  </si>
+  <si>
+    <t>Verifying PNG, another of the 4 stated allowed formats, is genuinely accepted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a valid .png file into a General Document slot
+3. Verify it is accepted into that slot's file list with no error</t>
+  </si>
+  <si>
+    <t>The PNG file should be accepted with no error.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: uploaded salarySlip.png into the empty PAN Card (General Documents) slot - accepted into the file list (salarySlip.png shown), no alert/error rendered. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a file exactly at the 5 MB size limit is accepted</t>
+  </si>
+  <si>
+    <t>Boundary test for "Max 5 MB per file" - a file exactly at 5,242,880 bytes should still be accepted (limit is a ceiling, not exclusive).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a file exactly 5,242,880 bytes (5 MB) into a document slot
+3. Verify it is accepted with no size-error message</t>
+  </si>
+  <si>
+    <t>A file exactly at the 5 MB limit should be accepted.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: uploaded exactly5mb.jpg (5,242,880 bytes exactly) into the Latest Photo (General Documents) slot - accepted into the file list, no size-error message rendered. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a file over the 5 MB size limit is rejected</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - a 6 MB file is rejected with a specific warning banner and is not added to the file list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a 6 MB file into a document slot
+3. Verify the warning message and that the file is not added to the list</t>
+  </si>
+  <si>
+    <t>Should be rejected with the message "The maximum file size is 5 MB." and not added to the file list.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: uploaded oversized.jpg (6,291,456 bytes) into the UAN Profile (General Documents) slot - rejected with the filedropper's own inline alert "The maximum file size is 5 MB." and NOT added to the file list (stayed empty). Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a filename over 256 characters is rejected</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - a 264-character filename is rejected with a specific popup naming the file. (Windows itself cannot store a file with such a long name, so automation constructs this file in-memory via Playwright's buffer-based upload rather than from a file on disk.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a file whose name is over 256 characters into a document slot
+3. Verify the resulting popup</t>
+  </si>
+  <si>
+    <t>Should be rejected with an "Information" popup: "&lt;filename&gt; Document is not uploaded as file name is too big" (OK).</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: uploaded a 264-character filename (in-memory buffer, valid image content) into the empty 10th (Qualification Documents) slot. Rejected with an Information popup: "&lt;filename&gt; Document is not uploaded as file name is too big" (OK) - exact wording matched, filename echoed correctly. File not added to the list. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a 2nd valid file is accepted into the same document slot</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - uploading a 2nd, distinct valid file into a slot that already holds one file is accepted (matches the "Max 2 files per document" policy).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload one valid file into a document slot
+3. Upload a second, different valid file into the same slot
+4. Verify both are accepted into that slot's file list</t>
+  </si>
+  <si>
+    <t>Both files should be accepted; the slot should now show 2 files.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: uploaded Aadhar.jpg then Aadhar2.jpg (2 distinct valid files) into the empty 12th (Qualification Documents) slot - both accepted, file list shows ["Aadhar.jpg","Aadhar2.jpg"] in order. Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify a document slot no longer accepts a 3rd file once it already holds 2</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - once a slot holds 2 files, its own "Choose File" input disappears from the page entirely (total file-input count on the page dropped from 13 to 12 after the 2nd upload into one slot), so a 3rd upload becomes impossible via the UI - no error message is needed since the control itself is gone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload 2 valid files into the same document slot
+3. Verify that slot's "Choose File" control is no longer present
+4. Verify no further file can be added to that slot</t>
+  </si>
+  <si>
+    <t>After 2 files, the slot's "Choose File" control should no longer be available - no 3rd file can be added.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads`: filled Highest Qualification (Qualification Documents) to 2 files (bsc.jpg, experience.jpg), then confirmed its "Choose File" control (the real input[type=file]) is gone entirely from that field's cell - count 0, matching Expected. RETRACTED (2026-09-28): an earlier note here flagged "Latest Photo" on `divorced` as already holding 2 files yet still showing an active Choose File control. Re-verified live and by the user's own manual check: this was a locator bug in the probing script (it picked up a DIFFERENT field's uploaded files by mistake) - "Latest Photo" on `divorced` genuinely has 0 files, so its Choose File control is correctly present. Not a defect.</t>
+  </si>
+  <si>
+    <t>Verify the Experience Documents field allows up to 10 files, not the standard 2-file limit</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet live-verified: the note text states "Max 2 files per document (except Experience documents: max 10)". Needs a dedicated live check uploading up to 10 valid files into the Experience Documents slot to confirm the higher cap actually applies there (and that a would-be 11th is blocked the same way a 3rd is blocked elsewhere).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" on an experienced=Yes account
+2. Upload 10 distinct valid files, one at a time, into the Experience Documents slot
+3. Verify all 10 are accepted
+4. Verify no 11th file can be added (its "Choose File" control disappears, matching the standard 2-file slots' behavior at their own cap)</t>
+  </si>
+  <si>
+    <t>To be confirmed live - the Experience Documents slot should accept up to 10 files and then behave like any other maxed-out slot.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `divorced` (experienced=Yes): Experience Documents slot started with 1 pre-existing file (12.jpg, from earlier manual/automated probing) and 9 more distinct valid files were uploaded one at a time (Aadhar.jpg, Pancard.jpg, samplepic.jpg, cheque.jpg, uan.jpg, 10.jpg, bsc.jpg, experience.jpg, test.pdf), all accepted, reaching exactly 10 total. At 10 files, the Choose File control (input[type=file]) is gone entirely from that field - no 11th file is possible. This is the FIRST live confirmation of the higher 10-file cap for Experience Documents (previously only stated in the note text). Matches Expected exactly - confirms the note text's claim is accurate.</t>
+  </si>
+  <si>
+    <t>Verify Submit is blocked when the consent checkbox is unchecked, regardless of document upload state</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - clicking Submit with the consent checkbox unchecked (even with zero documents uploaded) shows an "Information" popup. This is the FIRST gate checked, ahead of any per-document mandatory validation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Leave the consent checkbox unchecked
+3. Click Submit
+4. Verify the resulting popup</t>
+  </si>
+  <si>
+    <t>Should be rejected with an "Information" popup: "Please accept confirmation to proceed with the application" (OK). The page should remain on Upload Documents.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on `fresherUploads` (consent checkbox unchecked, default; various document slots already partially filled from TC_76-82): clicking Submit with consent unchecked showed an Information popup, exact wording "Please accept confirmation to proceed with the application" (OK), and the page remained on Upload Documents afterward (consent still unchecked, no navigation, no real submission). Matches Expected exactly.</t>
+  </si>
+  <si>
+    <t>Verify Submit is blocked when consent is checked but mandatory documents are still missing</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet live-verified: once the first gate (TC_84's consent check) is satisfied, it is not yet confirmed what Submit does with mandatory document slots still empty - per-slot messages, a single summary message, or something else.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Check the consent checkbox
+3. Leave one or more mandatory document slots empty
+4. Click Submit
+5. Verify the resulting message(s)</t>
+  </si>
+  <si>
+    <t>To be confirmed live - Submit should be rejected and should not proceed while any mandatory document is missing.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on fresherUploads: with consent checked and mandatory documents still missing, clicking Submit shows an "Information" popup: "Please upload all documents" (OK). Page stays on Upload Documents. This is a distinct message from the consent-unchecked gate (TC_84: "Please accept confirmation to proceed with the application") - the two gates are checked in order and each has its own message.</t>
+  </si>
+  <si>
+    <t>Verify the app does not flag the same file content being uploaded into two different document slots</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - the identical file, uploaded into both the Aadhaar Card slot and the PAN Card slot, produced no error, warning, or duplicate-detection message; both were silently accepted. User ruling (2026-09-25): this is a DEFECT - these are separate KYC/identity documents collected specifically so HR can verify identity, PAN and address independently; accepting the same file for two different document types defeats that purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload the exact same file into "Aadhaar Card"
+3. Upload the exact same file (identical bytes) into "PAN Card"
+4. Verify whether any duplicate-content warning appears</t>
+  </si>
+  <si>
+    <t>Uploading the same file content into two different document slots (e.g. Aadhaar Card and PAN Card) should be flagged/rejected, not silently accepted as two valid, independent documents.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-25 (initial probe). The identical file was accepted into both the Aadhaar Card and PAN Card slots with no warning of any kind. Confirmed as a defect by the user (2026-09-25).</t>
+  </si>
+  <si>
+    <t>Verify clicking Submit with every mandatory document uploaded and consent checked shows the submit confirmation</t>
+  </si>
+  <si>
+    <t>Confirmed by the user's own screenshot (2026-09-25) - once every mandatory document is uploaded and consent is checked, Submit shows a Yes/No confirmation dialog before anything is actually submitted.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1. with every mandatory document uploaded and consent checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" with every mandatory document uploaded and consent checked
+2. Click Submit
+3. Verify the confirmation dialog</t>
+  </si>
+  <si>
+    <t>Should show: "Are you sure you want to submit? Please ensure all the details are correct as you will not be able to edit these later." with Yes/No buttons. Nothing should be submitted yet.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Filled every remaining empty document slot on fresherUploads with a valid image, checked consent, clicked Submit. The confirmation dialog appeared as confirmed earlier by the user's own screenshot: "Are you sure you want to submit? Please ensure all the details are correct as you will not be able to edit these later." with Yes/No. Nothing was submitted yet (Submit itself was never clicked as Yes in this test).</t>
+  </si>
+  <si>
+    <t>Verify clicking "No" on the submit confirmation cancels without submitting</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet live-verified end-to-end (an automation attempt hit a DOM-index timing issue filling all 13 slots sequentially by position - needs a slot-filling approach keyed to each document's label rather than positional index, since the page's file inputs renumber as slots fill). Expected to be safe and non-destructive, unlike clicking "Yes".</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1. with every mandatory document uploaded and consent checked, reaching the confirmation dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "Are you sure you want to submit?" confirmation dialog (TC_87's precondition)
+2. Click "No"
+3. Verify the dialog closes without submitting
+4. Verify the candidate remains on Upload Documents with their uploaded documents intact</t>
+  </si>
+  <si>
+    <t>To be confirmed live - clicking "No" should cancel and leave Upload Documents exactly as before, with nothing submitted.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. From TC_87's confirmation dialog, clicked "No". The dialog closed, the candidate remained on Upload Documents (all 3 section headers still present), and the previously uploaded files were still shown as uploaded - nothing was lost or submitted.</t>
+  </si>
+  <si>
+    <t>Verify clicking "Yes" on the submit confirmation genuinely completes Phase 2</t>
+  </si>
+  <si>
+    <t>Confirmed by the user's own screenshots (2026-09-25). THIS TEST GENUINELY, IRREVERSIBLY SUBMITS THE APPLICATION - it must run ONLY on a fresh, single-use disposable account created just for this test, never on single/fresher/divorced or any other reusable pooled account, and never more than once per account. May trigger real backend workflows (HR visibility, scheduling, emails) beyond just this app's own state.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1, a fully valid "1. Other Details", and "2. Upload Documents" with every mandatory document uploaded and consent checked, on a FRESH, SINGLE-USE, disposable account created specifically for this test - reaching the confirmation dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the "Are you sure you want to submit?" confirmation dialog, on a disposable account, with every mandatory document uploaded and consent checked
+2. Click "Yes"
+3. Verify the resulting confirmation</t>
+  </si>
+  <si>
+    <t>Should show "Application Submitted" - "Congratulations! Your additional details have been submitted. Please attend the trainings that will be assigned to you." - with a journey graphic: "Application Form-Phase 1 Completed" (done), "Mankind to schedule Interviews", "Application Form-Phase 2 (Additional Information) Completed" (done), "Attend and complete your assigned training", "Welcome Onboard!" - and a Close button. This is the true end of the candidate flow for this account; do not attempt to reuse it afterwards.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28 (2nd attempt - the 1st attempt clicked Yes without waiting for the dialog to fully stabilize and produced an ambiguous result; a fresh disposable account was used for this careful re-run, the earlier one abandoned). Fresh disposable account (Aadhaar 916230533623, never reused): signup, Phase 1, Other Details all filled validly, a real successful Next to Upload Documents (zero validation messages), every mandatory slot filled, consent checked. Clicked Submit, waited explicitly for the Yes/No dialog to be visible and settled, clicked Yes. The "Application Submitted" modal appeared exactly as the user's own screenshots showed: "Congratulations! Your additional details have been submitted. Please attend the trainings that will be assigned to you." with the 5-step journey graphic (Phase 1 Completed, Mankind to schedule Interviews, Phase 2 Completed, Attend training, Welcome Onboard) and a Close button. Confirmed both via page text and a full-page screenshot. This account is now genuinely, irreversibly submitted - not reused for anything else.</t>
+  </si>
+  <si>
+    <t>Verify an already-uploaded file can be removed from a document slot before Submit</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet confirmed: it is not yet established whether the file-list widget offers a delete/remove control per uploaded file, or whether the only way to change a slot is via its remaining "Choose File" affordance (up to the 2-file cap).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a valid file into a document slot
+3. Look for a delete/remove control on the uploaded file's list entry
+4. If present, click it and verify the file is removed from the slot</t>
+  </si>
+  <si>
+    <t>To be confirmed live - determine whether a remove control exists and, if so, that it correctly removes only that file.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on fresherUploads: each uploaded file has a delete/remove icon (glyphicon-remove-circle). Clicking it shows a confirmation popup (Yes/OK); confirming removes the file (file count 1 -&gt; 0) and the "Choose File" control remains/returns available afterward. A remove control does exist, matching Expected.</t>
+  </si>
+  <si>
+    <t>Verify a file can be uploaded via drag-and-drop, not just "Choose File"</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet live-verified: the widget's own CSS class ("filedropper__dropzone") strongly implies drag-and-drop support in addition to the "Choose File" click path, but this has never been tested. Automating this needs a synthetic drop event (dispatching dragenter/dragover/drop with a DataTransfer holding a File), not a real OS drag gesture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Drag a valid file (e.g. Aadhar.jpg) onto a document slot's dropzone and drop it
+3. Verify the file is accepted into that slot's file list, the same as via "Choose File"</t>
+  </si>
+  <si>
+    <t>To be confirmed live - dropping a valid file onto the dropzone should be accepted identically to choosing it via the file picker.</t>
+  </si>
+  <si>
+    <t>Not yet automated. (Blocked: drag-and-drop needs a genuinely browser-trusted drag gesture, which a synthetic DOM event can't reliably simulate - needs a lower-level Chrome DevTools Protocol approach, not yet implemented.)</t>
+  </si>
+  <si>
+    <t>Verify a file whose real content does not match its claimed type/extension is still handled safely</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet conclusively live-verified: an attempt to upload a plain-text buffer disguised as "fake-image.jpg" with mimeType "image/jpeg" gave an inconclusive read (a selector issue on the automation side, not a confirmed app result) on whether it was added to the file list. The real-world risk this covers - a renamed executable or script passed off as an image - needs a clean re-check, and note that browser-side automation can only prove client-side (File.type/extension) behavior; whether the SERVER independently validates actual file content (magic bytes) is a separate, deeper question this suite cannot fully answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Upload a file whose actual bytes are not a real image/PDF, but whose name/extension is ".jpg" and whose declared type is "image/jpeg"
+3. Verify whether it is accepted into the file list or rejected
+4. If accepted, note this as a finding for a ruling on whether server-side content validation is needed</t>
+  </si>
+  <si>
+    <t>To be confirmed live - determine whether the app accepts a file based only on its name/declared type, or genuinely validates file content.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live on divorced (UAN Profile slot): a file whose real content is plain text (not a real image), named "fake-scan.jpg" with declared mimeType "image/jpeg", is accepted into the file list with NO error or warning of any kind. Confirms the app validates only the client-declared name/type, not actual file content (magic bytes). Whether the SERVER independently validates real file content on storage is a separate question this browser-level suite cannot verify. Flagged for a ruling: is accepting unverified content a defect worth raising, similar to TC_86 (duplicate-content), or an accepted limitation?</t>
+  </si>
+  <si>
+    <t>Verify a 3rd+ dependent, added via "Add Member" in 1.2 Dependent Details, also gets its own document-upload block</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet live-verified: TC_71/TC_72 only cover the default Father + Mother dependents. Whether a manually ADDED member (via "Add Member", not deceased) also gets a "{Name} - {Relation}'s Documents" block on Upload Documents has never been tested - needs a fresh account that adds a 3rd dependent and completes a fully valid Other Details submission.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1 and a fully, validly completed "1. Other Details" section with a successful Next click - the candidate is on Application Form - Phase 2, section "2. Upload Documents". Note: reaching this page requires a real successful Next on Other Details, which SAVES that data server-side (confirmed live for TC_62) - automation for this whole section must use a dedicated spare account, never the single/fresher pooled accounts used by section 1., on an account whose 1.2 Dependent Details has Father, Mother, AND one additional member added via "Add Member" (not deceased), before the successful Next that reaches Upload Documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" on an account with 3 non-deceased dependents (Father, Mother, and one added member)
+2. Verify "Click to Upload Dependent Documents" shows 3 blocks, one per dependent, each correctly headed and with Aadhaar Card* and Photo*</t>
+  </si>
+  <si>
+    <t>To be confirmed live - a manually added, non-deceased member should get its own document block, the same as Father/Mother.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Extended divorced with a 3rd dependent (Rohan Verma, Brother, DOB 15/08/1995) via Add Member, then a real successful Next (zero validation messages, form was already valid). Upload Documents now shows 3 dependent doc blocks: "Amandeep Singh - Father's Documents", "Kashish Kaur - Mother's Documents", "Rohan Verma - Brother's Documents" - a manually added, non-deceased member gets its own block, the same as Father/Mother.</t>
+  </si>
+  <si>
+    <t>Verify the step-indicator circle (not the label) navigates back from Upload Documents to Other Details</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-09-28 - the original premise ("no way back at all") was based on an incomplete earlier check that only tested the step LABEL text, not the step CIRCLE icon. Re-verified live: the "Other Details" step CIRCLE genuinely navigates back to Other Details with a normal, non-forced click (role="button", cursor:pointer, fully visible/enabled) - this is the SAME step-circle-click-to-navigate pattern used intentionally throughout the rest of this app, including Phase 1 (confirmed by the user). The step LABEL text alone is not clickable, and there is no dedicated "Back" button. This is correct, intentional app behavior, not a defect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Click the "Other Details" step LABEL text - verify nothing happens (still on Upload Documents)
+3. Click the "Other Details" step CIRCLE icon - verify it navigates back to "1. Other Details"
+4. Verify there is no dedicated "Back" button anywhere on Upload Documents</t>
+  </si>
+  <si>
+    <t>The step LABEL text should not be clickable. The step CIRCLE should navigate back to "1. Other Details" (consistent with the same step-indicator pattern used elsewhere in the app, e.g. Phase 1). There should be no dedicated "Back" button.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live: clicking the "Other Details" step LABEL does nothing (stays on Upload Documents). Clicking the step CIRCLE (normal click, not forced) navigates back to "1. Other Details" - Blood Group select reappears, Upload Documents section is gone. No dedicated "Back" button exists anywhere on the page. Matches the corrected Expected result.</t>
+  </si>
+  <si>
+    <t>Verify reloading "2. Upload Documents" loses any unsaved file selections</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-25 - after selecting a file into a slot (never saved/submitted) and reloading the page, the "Click to Upload ..." section headers were gone entirely (count 0), while the page title still read "Application Form - Phase 2". Since file selections only ever live in browser/client state until Submit, a reload re-derives the page from the last genuinely SAVED server state - for an account that has already completed Other Details, that appears to be Other Details itself, not Upload Documents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents"
+2. Select a valid file into a document slot (do not click Submit)
+3. Reload the page
+4. Verify the selected file is gone and the page no longer shows the Upload Documents sections</t>
+  </si>
+  <si>
+    <t>A reload should lose any unsaved file selection, and should not leave the candidate on a half-populated Upload Documents page - it should re-render from the last saved state.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. Confirmed live: with a file selected into a slot but not submitted, reloading the page results in zero "Click to Upload ..." section headers being present (title still reads Application Form - Phase 2). The page re-derives from the last genuinely SAVED server state - for an account that has already completed Other Details, that is Other Details itself, not a half-populated Upload Documents page. The selected file is gone.</t>
+  </si>
+  <si>
+    <t>Verify double-clicking Submit does not cause a double submission</t>
+  </si>
+  <si>
+    <t>FLAGGED, not yet live-verified: rapidly double-clicking Submit on a fully valid form could risk two confirmation flows or a race condition submitting the application twice. This must be tested carefully, on a fresh single-use disposable account (like TC_89), and the double-click must be tried in a way that cannot accidentally complete two real submissions.</t>
+  </si>
+  <si>
+    <t>Reached via a genuinely completed Phase 1, a fully valid "1. Other Details", and "2. Upload Documents" with every mandatory document uploaded and consent checked, on a FRESH, SINGLE-USE, disposable account created specifically for this test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach "2. Upload Documents" with every mandatory document uploaded and consent checked, on a disposable account
+2. Double-click Submit rapidly
+3. Verify only one confirmation dialog appears
+4. If "Yes" is then clicked once, verify only one successful submission occurs, not two</t>
+  </si>
+  <si>
+    <t>To be confirmed live - a double-click on Submit should not produce two confirmation dialogs or two completed submissions.</t>
+  </si>
+  <si>
+    <t>Automated 2026-09-28. With every mandatory slot filled and consent checked, double-clicked Submit rapidly. Only ONE Yes/No confirmation dialog appeared (not two) - no risk of a duplicated confirmation flow. Clicked No to cancel safely; confirmed still on Upload Documents afterward, nothing was ever submitted. This test intentionally never clicks "Yes", since the core risk (a doubled confirmation/submission path) is fully verifiable without a real submission - no disposable account was needed.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -2642,20 +4364,26 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
       <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2674,6 +4402,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2687,7 +4421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2715,6 +4449,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2996,7 +4731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K120"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -3044,7 +4779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3076,7 +4811,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3108,7 +4843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="255" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="255" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3143,7 +4878,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3175,7 +4910,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3207,7 +4942,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3239,7 +4974,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3271,7 +5006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3303,7 +5038,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3335,7 +5070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3367,7 +5102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3399,7 +5134,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3431,7 +5166,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3463,7 +5198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3495,7 +5230,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3527,7 +5262,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3559,7 +5294,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3591,7 +5326,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3623,7 +5358,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3655,7 +5390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3687,7 +5422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3719,7 +5454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3751,7 +5486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3783,7 +5518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3815,7 +5550,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="90" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3847,7 +5582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3879,7 +5614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3911,7 +5646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3943,7 +5678,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="7" customFormat="1" ht="225" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="225" customHeight="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3975,7 +5710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="120" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4007,7 +5742,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4039,7 +5774,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4071,7 +5806,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4103,7 +5838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4135,7 +5870,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4167,7 +5902,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4199,7 +5934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4231,7 +5966,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="120" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4263,7 +5998,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="4" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="90" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -4298,7 +6033,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4330,7 +6065,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="4" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="105" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -4365,7 +6100,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="4" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="105" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -4400,7 +6135,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4432,7 +6167,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4464,7 +6199,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4496,7 +6231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4528,7 +6263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="7" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="180" customHeight="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4560,7 +6295,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4592,7 +6327,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4624,7 +6359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4656,7 +6391,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="10" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="120" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>51</v>
       </c>
@@ -4691,7 +6426,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="10" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="165" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>52</v>
       </c>
@@ -4726,7 +6461,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>53</v>
       </c>
@@ -4761,7 +6496,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>54</v>
       </c>
@@ -4796,7 +6531,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>55</v>
       </c>
@@ -4831,7 +6566,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>56</v>
       </c>
@@ -4866,7 +6601,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>57</v>
       </c>
@@ -4901,7 +6636,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>58</v>
       </c>
@@ -4936,7 +6671,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="4" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="210" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -4971,7 +6706,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="10" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="120" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>60</v>
       </c>
@@ -5006,7 +6741,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>61</v>
       </c>
@@ -5041,7 +6776,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="10" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="45" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>62</v>
       </c>
@@ -5076,7 +6811,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>63</v>
       </c>
@@ -5111,7 +6846,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="60" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -5146,7 +6881,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="4" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="90" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -5181,7 +6916,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>66</v>
       </c>
@@ -5216,7 +6951,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>67</v>
       </c>
@@ -5251,7 +6986,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>68</v>
       </c>
@@ -5286,7 +7021,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>69</v>
       </c>
@@ -5321,7 +7056,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="71" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>70</v>
       </c>
@@ -5356,7 +7091,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>71</v>
       </c>
@@ -5391,7 +7126,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="10" customFormat="1" ht="375" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="375" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>72</v>
       </c>
@@ -5426,7 +7161,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="10" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="45" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>73</v>
       </c>
@@ -5461,7 +7196,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>74</v>
       </c>
@@ -5496,7 +7231,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>75</v>
       </c>
@@ -5531,7 +7266,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>76</v>
       </c>
@@ -5566,7 +7301,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="60" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -5601,7 +7336,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>78</v>
       </c>
@@ -5636,7 +7371,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>79</v>
       </c>
@@ -5671,7 +7406,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="10" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="105" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>80</v>
       </c>
@@ -5706,7 +7441,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="60" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>81</v>
       </c>
@@ -5741,7 +7476,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="83" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>82</v>
       </c>
@@ -5776,7 +7511,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="84" spans="1:11" s="10" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="105" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>83</v>
       </c>
@@ -5811,7 +7546,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="85" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>84</v>
       </c>
@@ -5846,7 +7581,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>85</v>
       </c>
@@ -5881,7 +7616,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="87" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>86</v>
       </c>
@@ -5916,7 +7651,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>87</v>
       </c>
@@ -5951,7 +7686,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="89" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>88</v>
       </c>
@@ -5986,7 +7721,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="90" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>89</v>
       </c>
@@ -6021,7 +7756,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="91" spans="1:11" s="10" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="120" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>90</v>
       </c>
@@ -6056,7 +7791,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="10" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="150" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>91</v>
       </c>
@@ -6091,7 +7826,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="93" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>92</v>
       </c>
@@ -6126,7 +7861,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="210" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>93</v>
       </c>
@@ -6161,7 +7896,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>94</v>
       </c>
@@ -6196,7 +7931,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="96" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>95</v>
       </c>
@@ -6231,7 +7966,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>96</v>
       </c>
@@ -6266,7 +8001,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>97</v>
       </c>
@@ -6301,7 +8036,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="99" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>98</v>
       </c>
@@ -6336,7 +8071,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="100" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>99</v>
       </c>
@@ -6371,7 +8106,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="101" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>100</v>
       </c>
@@ -6406,7 +8141,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="102" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>101</v>
       </c>
@@ -6441,7 +8176,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="103" spans="1:11" s="4" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="75" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -6476,7 +8211,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>103</v>
       </c>
@@ -6511,7 +8246,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="105" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>104</v>
       </c>
@@ -6546,7 +8281,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>105</v>
       </c>
@@ -6581,7 +8316,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="107" spans="1:11" s="10" customFormat="1" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="135" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>106</v>
       </c>
@@ -6616,7 +8351,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="108" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>107</v>
       </c>
@@ -6651,7 +8386,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>108</v>
       </c>
@@ -6686,7 +8421,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="4" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="75" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -6721,7 +8456,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>110</v>
       </c>
@@ -6756,7 +8491,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="112" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>111</v>
       </c>
@@ -6791,7 +8526,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="113" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>112</v>
       </c>
@@ -6826,7 +8561,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="114" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>113</v>
       </c>
@@ -6861,7 +8596,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="115" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10">
         <v>114</v>
       </c>
@@ -6896,7 +8631,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="116" spans="1:11" s="10" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="75" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="10">
         <v>115</v>
       </c>
@@ -6931,7 +8666,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="117" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="10">
         <v>116</v>
       </c>
@@ -6966,7 +8701,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="118" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="10">
         <v>117</v>
       </c>
@@ -7001,7 +8736,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="119" spans="1:11" s="10" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="90" customHeight="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10">
         <v>118</v>
       </c>
@@ -7036,7 +8771,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="300" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="300" customHeight="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>119</v>
       </c>
@@ -7073,14 +8808,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K97"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -7128,8 +8863,3278 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D2" t="s">
+        <v>745</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>746</v>
+      </c>
+      <c r="G2" t="s">
+        <v>747</v>
+      </c>
+      <c r="H2" t="s">
+        <v>748</v>
+      </c>
+      <c r="I2" t="s">
+        <v>749</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>746</v>
+      </c>
+      <c r="G3" t="s">
+        <v>752</v>
+      </c>
+      <c r="H3" t="s">
+        <v>753</v>
+      </c>
+      <c r="I3" t="s">
+        <v>754</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>755</v>
+      </c>
+      <c r="D4" t="s">
+        <v>756</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>746</v>
+      </c>
+      <c r="G4" t="s">
+        <v>757</v>
+      </c>
+      <c r="H4" t="s">
+        <v>758</v>
+      </c>
+      <c r="I4" t="s">
+        <v>759</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>760</v>
+      </c>
+      <c r="D5" t="s">
+        <v>761</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>746</v>
+      </c>
+      <c r="G5" t="s">
+        <v>762</v>
+      </c>
+      <c r="H5" t="s">
+        <v>763</v>
+      </c>
+      <c r="I5" t="s">
+        <v>764</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>765</v>
+      </c>
+      <c r="D6" t="s">
+        <v>766</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>746</v>
+      </c>
+      <c r="G6" t="s">
+        <v>767</v>
+      </c>
+      <c r="H6" t="s">
+        <v>768</v>
+      </c>
+      <c r="I6" t="s">
+        <v>769</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>770</v>
+      </c>
+      <c r="D7" t="s">
+        <v>771</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>746</v>
+      </c>
+      <c r="G7" t="s">
+        <v>772</v>
+      </c>
+      <c r="H7" t="s">
+        <v>773</v>
+      </c>
+      <c r="I7" t="s">
+        <v>774</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>775</v>
+      </c>
+      <c r="D8" t="s">
+        <v>776</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>746</v>
+      </c>
+      <c r="G8" t="s">
+        <v>777</v>
+      </c>
+      <c r="H8" t="s">
+        <v>778</v>
+      </c>
+      <c r="I8" t="s">
+        <v>779</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>780</v>
+      </c>
+      <c r="D9" t="s">
+        <v>781</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>782</v>
+      </c>
+      <c r="G9" t="s">
+        <v>783</v>
+      </c>
+      <c r="H9" t="s">
+        <v>784</v>
+      </c>
+      <c r="I9" t="s">
+        <v>785</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>786</v>
+      </c>
+      <c r="D10" t="s">
+        <v>787</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>788</v>
+      </c>
+      <c r="G10" t="s">
+        <v>789</v>
+      </c>
+      <c r="H10" t="s">
+        <v>790</v>
+      </c>
+      <c r="I10" t="s">
+        <v>791</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>797</v>
+      </c>
+      <c r="D12" t="s">
+        <v>798</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>788</v>
+      </c>
+      <c r="G12" t="s">
+        <v>799</v>
+      </c>
+      <c r="H12" t="s">
+        <v>800</v>
+      </c>
+      <c r="I12" t="s">
+        <v>801</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>802</v>
+      </c>
+      <c r="D13" t="s">
+        <v>803</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>746</v>
+      </c>
+      <c r="G13" t="s">
+        <v>804</v>
+      </c>
+      <c r="H13" t="s">
+        <v>597</v>
+      </c>
+      <c r="I13" t="s">
+        <v>805</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
+        <v>806</v>
+      </c>
+      <c r="D14" t="s">
+        <v>807</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>808</v>
+      </c>
+      <c r="G14" t="s">
+        <v>809</v>
+      </c>
+      <c r="H14" t="s">
+        <v>810</v>
+      </c>
+      <c r="I14" t="s">
+        <v>811</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>812</v>
+      </c>
+      <c r="D15" t="s">
+        <v>813</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>808</v>
+      </c>
+      <c r="G15" t="s">
+        <v>814</v>
+      </c>
+      <c r="H15" t="s">
+        <v>597</v>
+      </c>
+      <c r="I15" t="s">
+        <v>815</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>816</v>
+      </c>
+      <c r="D16" t="s">
+        <v>817</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>808</v>
+      </c>
+      <c r="G16" t="s">
+        <v>818</v>
+      </c>
+      <c r="H16" t="s">
+        <v>819</v>
+      </c>
+      <c r="I16" t="s">
+        <v>820</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="s">
+        <v>821</v>
+      </c>
+      <c r="D17" t="s">
+        <v>822</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>808</v>
+      </c>
+      <c r="G17" t="s">
+        <v>823</v>
+      </c>
+      <c r="H17" t="s">
+        <v>824</v>
+      </c>
+      <c r="I17" t="s">
+        <v>825</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
+        <v>826</v>
+      </c>
+      <c r="D18" t="s">
+        <v>827</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>808</v>
+      </c>
+      <c r="G18" t="s">
+        <v>828</v>
+      </c>
+      <c r="H18" t="s">
+        <v>829</v>
+      </c>
+      <c r="I18" t="s">
+        <v>830</v>
+      </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>831</v>
+      </c>
+      <c r="D19" t="s">
+        <v>832</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>808</v>
+      </c>
+      <c r="G19" t="s">
+        <v>833</v>
+      </c>
+      <c r="H19" t="s">
+        <v>834</v>
+      </c>
+      <c r="I19" t="s">
+        <v>835</v>
+      </c>
+      <c r="J19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" t="s">
+        <v>836</v>
+      </c>
+      <c r="D20" t="s">
+        <v>837</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>808</v>
+      </c>
+      <c r="G20" t="s">
+        <v>838</v>
+      </c>
+      <c r="H20" t="s">
+        <v>839</v>
+      </c>
+      <c r="I20" t="s">
+        <v>840</v>
+      </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>841</v>
+      </c>
+      <c r="D21" t="s">
+        <v>842</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>808</v>
+      </c>
+      <c r="G21" t="s">
+        <v>843</v>
+      </c>
+      <c r="H21" t="s">
+        <v>844</v>
+      </c>
+      <c r="I21" t="s">
+        <v>845</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>846</v>
+      </c>
+      <c r="D22" t="s">
+        <v>847</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>808</v>
+      </c>
+      <c r="G22" t="s">
+        <v>848</v>
+      </c>
+      <c r="H22" t="s">
+        <v>849</v>
+      </c>
+      <c r="I22" t="s">
+        <v>850</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" t="s">
+        <v>851</v>
+      </c>
+      <c r="D23" t="s">
+        <v>852</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>808</v>
+      </c>
+      <c r="G23" t="s">
+        <v>853</v>
+      </c>
+      <c r="H23" t="s">
+        <v>854</v>
+      </c>
+      <c r="I23" t="s">
+        <v>855</v>
+      </c>
+      <c r="J23" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" t="s">
+        <v>856</v>
+      </c>
+      <c r="D24" t="s">
+        <v>857</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>808</v>
+      </c>
+      <c r="G24" t="s">
+        <v>858</v>
+      </c>
+      <c r="H24" t="s">
+        <v>859</v>
+      </c>
+      <c r="I24" t="s">
+        <v>860</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" t="s">
+        <v>861</v>
+      </c>
+      <c r="D25" t="s">
+        <v>862</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
+        <v>808</v>
+      </c>
+      <c r="G25" t="s">
+        <v>863</v>
+      </c>
+      <c r="H25" t="s">
+        <v>864</v>
+      </c>
+      <c r="I25" t="s">
+        <v>865</v>
+      </c>
+      <c r="J25" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" t="s">
+        <v>866</v>
+      </c>
+      <c r="D26" t="s">
+        <v>867</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>808</v>
+      </c>
+      <c r="G26" t="s">
+        <v>868</v>
+      </c>
+      <c r="H26" t="s">
+        <v>869</v>
+      </c>
+      <c r="I26" t="s">
+        <v>870</v>
+      </c>
+      <c r="J26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" t="s">
+        <v>871</v>
+      </c>
+      <c r="D27" t="s">
+        <v>872</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>808</v>
+      </c>
+      <c r="G27" t="s">
+        <v>873</v>
+      </c>
+      <c r="H27" t="s">
+        <v>874</v>
+      </c>
+      <c r="I27" t="s">
+        <v>875</v>
+      </c>
+      <c r="J27" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" t="s">
+        <v>876</v>
+      </c>
+      <c r="D28" t="s">
+        <v>877</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>808</v>
+      </c>
+      <c r="G28" t="s">
+        <v>878</v>
+      </c>
+      <c r="H28" t="s">
+        <v>879</v>
+      </c>
+      <c r="I28" t="s">
+        <v>880</v>
+      </c>
+      <c r="J28" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" t="s">
+        <v>881</v>
+      </c>
+      <c r="D29" t="s">
+        <v>882</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>808</v>
+      </c>
+      <c r="G29" t="s">
+        <v>883</v>
+      </c>
+      <c r="H29" t="s">
+        <v>884</v>
+      </c>
+      <c r="I29" t="s">
+        <v>885</v>
+      </c>
+      <c r="J29" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" t="s">
+        <v>886</v>
+      </c>
+      <c r="D30" t="s">
+        <v>887</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>808</v>
+      </c>
+      <c r="G30" t="s">
+        <v>888</v>
+      </c>
+      <c r="H30" t="s">
+        <v>889</v>
+      </c>
+      <c r="I30" t="s">
+        <v>890</v>
+      </c>
+      <c r="J30" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" t="s">
+        <v>891</v>
+      </c>
+      <c r="D31" t="s">
+        <v>892</v>
+      </c>
+      <c r="E31" t="s">
+        <v>499</v>
+      </c>
+      <c r="F31" t="s">
+        <v>808</v>
+      </c>
+      <c r="G31" t="s">
+        <v>893</v>
+      </c>
+      <c r="H31" t="s">
+        <v>894</v>
+      </c>
+      <c r="I31" t="s">
+        <v>895</v>
+      </c>
+      <c r="J31" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" t="s">
+        <v>896</v>
+      </c>
+      <c r="D32" t="s">
+        <v>897</v>
+      </c>
+      <c r="E32" t="s">
+        <v>524</v>
+      </c>
+      <c r="F32" t="s">
+        <v>808</v>
+      </c>
+      <c r="G32" t="s">
+        <v>898</v>
+      </c>
+      <c r="H32" t="s">
+        <v>718</v>
+      </c>
+      <c r="I32" t="s">
+        <v>899</v>
+      </c>
+      <c r="J32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" t="s">
+        <v>900</v>
+      </c>
+      <c r="D33" t="s">
+        <v>901</v>
+      </c>
+      <c r="E33" t="s">
+        <v>524</v>
+      </c>
+      <c r="F33" t="s">
+        <v>808</v>
+      </c>
+      <c r="G33" t="s">
+        <v>902</v>
+      </c>
+      <c r="H33" t="s">
+        <v>903</v>
+      </c>
+      <c r="I33" t="s">
+        <v>904</v>
+      </c>
+      <c r="J33" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" t="s">
+        <v>905</v>
+      </c>
+      <c r="D34" t="s">
+        <v>906</v>
+      </c>
+      <c r="E34" t="s">
+        <v>499</v>
+      </c>
+      <c r="F34" t="s">
+        <v>808</v>
+      </c>
+      <c r="G34" t="s">
+        <v>907</v>
+      </c>
+      <c r="H34" t="s">
+        <v>908</v>
+      </c>
+      <c r="I34" t="s">
+        <v>909</v>
+      </c>
+      <c r="J34" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" t="s">
+        <v>910</v>
+      </c>
+      <c r="D35" t="s">
+        <v>911</v>
+      </c>
+      <c r="E35" t="s">
+        <v>499</v>
+      </c>
+      <c r="F35" t="s">
+        <v>808</v>
+      </c>
+      <c r="G35" t="s">
+        <v>912</v>
+      </c>
+      <c r="H35" t="s">
+        <v>913</v>
+      </c>
+      <c r="I35" t="s">
+        <v>914</v>
+      </c>
+      <c r="J35" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" t="s">
+        <v>920</v>
+      </c>
+      <c r="D37" t="s">
+        <v>921</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>808</v>
+      </c>
+      <c r="G37" t="s">
+        <v>922</v>
+      </c>
+      <c r="H37" t="s">
+        <v>597</v>
+      </c>
+      <c r="I37" t="s">
+        <v>923</v>
+      </c>
+      <c r="J37" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C38" t="s">
+        <v>924</v>
+      </c>
+      <c r="D38" t="s">
+        <v>925</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>808</v>
+      </c>
+      <c r="G38" t="s">
+        <v>926</v>
+      </c>
+      <c r="H38" t="s">
+        <v>927</v>
+      </c>
+      <c r="I38" t="s">
+        <v>928</v>
+      </c>
+      <c r="J38" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" t="s">
+        <v>929</v>
+      </c>
+      <c r="D39" t="s">
+        <v>930</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>808</v>
+      </c>
+      <c r="G39" t="s">
+        <v>931</v>
+      </c>
+      <c r="H39" t="s">
+        <v>932</v>
+      </c>
+      <c r="I39" t="s">
+        <v>933</v>
+      </c>
+      <c r="J39" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40" t="s">
+        <v>934</v>
+      </c>
+      <c r="D40" t="s">
+        <v>935</v>
+      </c>
+      <c r="E40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" t="s">
+        <v>808</v>
+      </c>
+      <c r="G40" t="s">
+        <v>936</v>
+      </c>
+      <c r="H40" t="s">
+        <v>937</v>
+      </c>
+      <c r="I40" t="s">
+        <v>938</v>
+      </c>
+      <c r="J40" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" t="s">
+        <v>939</v>
+      </c>
+      <c r="D41" t="s">
+        <v>940</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>808</v>
+      </c>
+      <c r="G41" t="s">
+        <v>941</v>
+      </c>
+      <c r="H41" t="s">
+        <v>942</v>
+      </c>
+      <c r="I41" t="s">
+        <v>943</v>
+      </c>
+      <c r="J41" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" t="s">
+        <v>944</v>
+      </c>
+      <c r="D42" t="s">
+        <v>945</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>808</v>
+      </c>
+      <c r="G42" t="s">
+        <v>946</v>
+      </c>
+      <c r="H42" t="s">
+        <v>947</v>
+      </c>
+      <c r="I42" t="s">
+        <v>948</v>
+      </c>
+      <c r="J42" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" t="s">
+        <v>949</v>
+      </c>
+      <c r="D43" t="s">
+        <v>950</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>808</v>
+      </c>
+      <c r="G43" t="s">
+        <v>951</v>
+      </c>
+      <c r="H43" t="s">
+        <v>952</v>
+      </c>
+      <c r="I43" t="s">
+        <v>953</v>
+      </c>
+      <c r="J43" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" t="s">
+        <v>954</v>
+      </c>
+      <c r="D44" t="s">
+        <v>955</v>
+      </c>
+      <c r="E44" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" t="s">
+        <v>808</v>
+      </c>
+      <c r="G44" t="s">
+        <v>956</v>
+      </c>
+      <c r="H44" t="s">
+        <v>957</v>
+      </c>
+      <c r="I44" t="s">
+        <v>958</v>
+      </c>
+      <c r="J44" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>278</v>
+      </c>
+      <c r="C45" t="s">
+        <v>959</v>
+      </c>
+      <c r="D45" t="s">
+        <v>960</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>961</v>
+      </c>
+      <c r="G45" t="s">
+        <v>962</v>
+      </c>
+      <c r="H45" t="s">
+        <v>963</v>
+      </c>
+      <c r="I45" t="s">
+        <v>964</v>
+      </c>
+      <c r="J45" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>284</v>
+      </c>
+      <c r="C46" t="s">
+        <v>965</v>
+      </c>
+      <c r="D46" t="s">
+        <v>966</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>967</v>
+      </c>
+      <c r="G46" t="s">
+        <v>968</v>
+      </c>
+      <c r="H46" t="s">
+        <v>969</v>
+      </c>
+      <c r="I46" t="s">
+        <v>970</v>
+      </c>
+      <c r="J46" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C47" t="s">
+        <v>971</v>
+      </c>
+      <c r="D47" t="s">
+        <v>972</v>
+      </c>
+      <c r="E47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" t="s">
+        <v>808</v>
+      </c>
+      <c r="G47" t="s">
+        <v>973</v>
+      </c>
+      <c r="H47" t="s">
+        <v>974</v>
+      </c>
+      <c r="I47" t="s">
+        <v>975</v>
+      </c>
+      <c r="J47" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>296</v>
+      </c>
+      <c r="C48" t="s">
+        <v>976</v>
+      </c>
+      <c r="D48" t="s">
+        <v>977</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" t="s">
+        <v>808</v>
+      </c>
+      <c r="G48" t="s">
+        <v>978</v>
+      </c>
+      <c r="H48" t="s">
+        <v>979</v>
+      </c>
+      <c r="I48" t="s">
+        <v>980</v>
+      </c>
+      <c r="J48" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>302</v>
+      </c>
+      <c r="C49" t="s">
+        <v>981</v>
+      </c>
+      <c r="D49" t="s">
+        <v>982</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>808</v>
+      </c>
+      <c r="G49" t="s">
+        <v>983</v>
+      </c>
+      <c r="H49" t="s">
+        <v>984</v>
+      </c>
+      <c r="I49" t="s">
+        <v>985</v>
+      </c>
+      <c r="J49" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13">
+        <v>49</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" t="s">
+        <v>992</v>
+      </c>
+      <c r="D51" t="s">
+        <v>993</v>
+      </c>
+      <c r="E51" t="s">
+        <v>524</v>
+      </c>
+      <c r="F51" t="s">
+        <v>808</v>
+      </c>
+      <c r="G51" t="s">
+        <v>994</v>
+      </c>
+      <c r="H51" t="s">
+        <v>995</v>
+      </c>
+      <c r="I51" t="s">
+        <v>996</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>320</v>
+      </c>
+      <c r="C52" t="s">
+        <v>997</v>
+      </c>
+      <c r="D52" t="s">
+        <v>998</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>808</v>
+      </c>
+      <c r="G52" t="s">
+        <v>999</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J52" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>328</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
+        <v>808</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H53" t="s">
+        <v>597</v>
+      </c>
+      <c r="I53" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J53" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>334</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E54" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" t="s">
+        <v>808</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H54" t="s">
+        <v>829</v>
+      </c>
+      <c r="I54" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J54" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>340</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" t="s">
+        <v>808</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H55" t="s">
+        <v>834</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J55" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>346</v>
+      </c>
+      <c r="C56" t="s">
+        <v>846</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>808</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I56" t="s">
+        <v>1017</v>
+      </c>
+      <c r="J56" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>352</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E57" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" t="s">
+        <v>808</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I57" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>358</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E58" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" t="s">
+        <v>808</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I58" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>364</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s">
+        <v>808</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>370</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E60" t="s">
+        <v>499</v>
+      </c>
+      <c r="F60" t="s">
+        <v>808</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>382</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E62" t="s">
+        <v>524</v>
+      </c>
+      <c r="F62" t="s">
+        <v>808</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H62" t="s">
+        <v>718</v>
+      </c>
+      <c r="I62" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J62" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>388</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" t="s">
+        <v>808</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J63" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>394</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>808</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J64" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>400</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E65" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" t="s">
+        <v>808</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I65" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>406</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I66" t="s">
+        <v>1068</v>
+      </c>
+      <c r="J66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>412</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I67" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>418</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I68" t="s">
+        <v>1078</v>
+      </c>
+      <c r="J68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>424</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I69" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>430</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1088</v>
+      </c>
+      <c r="I70" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>436</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I71" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>442</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I72" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>448</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I73" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>454</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I74" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>466</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E76" t="s">
+        <v>524</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>472</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I77" t="s">
+        <v>1126</v>
+      </c>
+      <c r="J77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>478</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I78" t="s">
+        <v>1131</v>
+      </c>
+      <c r="J78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>484</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E79" t="s">
+        <v>499</v>
+      </c>
+      <c r="F79" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I79" t="s">
+        <v>1136</v>
+      </c>
+      <c r="J79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>490</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E80" t="s">
+        <v>499</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I80" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>496</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E81" t="s">
+        <v>524</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H81" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>503</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E82" t="s">
+        <v>499</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H82" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1151</v>
+      </c>
+      <c r="J82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>509</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E83" t="s">
+        <v>499</v>
+      </c>
+      <c r="F83" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H83" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1156</v>
+      </c>
+      <c r="J83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>515</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E84" t="s">
+        <v>499</v>
+      </c>
+      <c r="F84" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H84" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I84" t="s">
+        <v>1161</v>
+      </c>
+      <c r="J84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>521</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E85" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H85" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I85" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>528</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E86" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H86" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I86" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>540</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I88" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>546</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E89" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G89" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I89" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>553</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E90" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H90" t="s">
+        <v>1193</v>
+      </c>
+      <c r="I90" t="s">
+        <v>1194</v>
+      </c>
+      <c r="J90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>560</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E91" t="s">
+        <v>499</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H91" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I91" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>567</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E92" t="s">
+        <v>499</v>
+      </c>
+      <c r="F92" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J92" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>581</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H94" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>587</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E95" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>593</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E96" t="s">
+        <v>499</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>599</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E97" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J97" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>